--- a/files/DC-ORDERDATEI 1025.xlsx_.xlsx
+++ b/files/DC-ORDERDATEI 1025.xlsx_.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,32 +425,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MgCode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
@@ -471,7 +459,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>OCT250001</t>
+          <t>OCT250338</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,7 +486,7 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>OCT250002</t>
+          <t>OCT250339</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -525,7 +513,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>OCT250003</t>
+          <t>OCT250340</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,7 +540,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>OCT250004</t>
+          <t>OCT250341</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,7 +567,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>OCT250005</t>
+          <t>OCT250342</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,7 +594,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>OCT250006</t>
+          <t>OCT250343</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -633,7 +621,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>OCT250007</t>
+          <t>OCT250344</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -660,7 +648,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>OCT250008</t>
+          <t>OCT250345</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -687,7 +675,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>OCT250009</t>
+          <t>OCT250346</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +702,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>OCT250010</t>
+          <t>OCT250347</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -741,7 +729,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>OCT250011</t>
+          <t>OCT250348</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -768,7 +756,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>OCT250012</t>
+          <t>OCT250349</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -795,7 +783,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>OCT250013</t>
+          <t>OCT250350</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -822,7 +810,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>OCT250014</t>
+          <t>OCT250351</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -849,7 +837,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>OCT250015</t>
+          <t>OCT250352</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -876,7 +864,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>OCT250016</t>
+          <t>OCT250353</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -903,7 +891,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>OCT250017</t>
+          <t>OCT250354</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -930,7 +918,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>OCT250018</t>
+          <t>OCT250355</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -957,7 +945,7 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>OCT250019</t>
+          <t>OCT250356</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -984,7 +972,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>OCT250020</t>
+          <t>OCT250357</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1011,7 +999,7 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>OCT250021</t>
+          <t>OCT250358</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1038,7 +1026,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>OCT250022</t>
+          <t>OCT250359</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1065,7 +1053,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>OCT250023</t>
+          <t>OCT250360</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1092,7 +1080,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>OCT250024</t>
+          <t>OCT250361</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1119,7 +1107,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>OCT250025</t>
+          <t>OCT250362</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1146,7 +1134,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>OCT250026</t>
+          <t>OCT250363</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,7 +1161,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>OCT250027</t>
+          <t>OCT250364</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1200,7 +1188,7 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>OCT250028</t>
+          <t>OCT250365</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1227,7 +1215,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>OCT250029</t>
+          <t>OCT250366</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1254,7 +1242,7 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>OCT250030</t>
+          <t>OCT250367</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1281,7 +1269,7 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>OCT250031</t>
+          <t>OCT250368</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1308,7 +1296,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>OCT250032</t>
+          <t>OCT250369</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1335,7 +1323,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>OCT250033</t>
+          <t>OCT250370</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1362,7 +1350,7 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>OCT250034</t>
+          <t>OCT250371</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1389,7 +1377,7 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>OCT250035</t>
+          <t>OCT250372</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1416,7 +1404,7 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>OCT250036</t>
+          <t>OCT250373</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1443,7 +1431,7 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>OCT250037</t>
+          <t>OCT250374</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1470,7 +1458,7 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>OCT250038</t>
+          <t>OCT250375</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1497,7 +1485,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>OCT250039</t>
+          <t>OCT250376</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1524,7 +1512,7 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>OCT250040</t>
+          <t>OCT250377</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1551,7 +1539,7 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>OCT250041</t>
+          <t>OCT250378</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1578,7 +1566,7 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>OCT250042</t>
+          <t>OCT250379</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1605,7 +1593,7 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>OCT250043</t>
+          <t>OCT250380</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1632,7 +1620,7 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>OCT250044</t>
+          <t>OCT250381</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1659,7 +1647,7 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>OCT250045</t>
+          <t>OCT250382</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1686,7 +1674,7 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>OCT250046</t>
+          <t>OCT250383</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1713,7 +1701,7 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>OCT250047</t>
+          <t>OCT250384</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1740,7 +1728,7 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>OCT250048</t>
+          <t>OCT250385</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1767,7 +1755,7 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>OCT250049</t>
+          <t>OCT250386</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1794,7 +1782,7 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>OCT250050</t>
+          <t>OCT250387</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1821,7 +1809,7 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>OCT250051</t>
+          <t>OCT250388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1848,7 +1836,7 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>OCT250052</t>
+          <t>OCT250389</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1875,7 +1863,7 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>OCT250053</t>
+          <t>OCT250390</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1902,7 +1890,7 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>OCT250054</t>
+          <t>OCT250391</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1929,7 +1917,7 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>OCT250055</t>
+          <t>OCT250392</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1956,7 +1944,7 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>OCT250056</t>
+          <t>OCT250393</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1983,7 +1971,7 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>OCT250057</t>
+          <t>OCT250394</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2010,7 +1998,7 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>OCT250058</t>
+          <t>OCT250395</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2037,7 +2025,7 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>OCT250059</t>
+          <t>OCT250396</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2064,7 +2052,7 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>OCT250060</t>
+          <t>OCT250397</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2091,7 +2079,7 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>OCT250061</t>
+          <t>OCT250398</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2118,7 +2106,7 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>OCT250062</t>
+          <t>OCT250399</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2145,7 +2133,7 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>OCT250063</t>
+          <t>OCT250400</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2172,7 +2160,7 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>OCT250064</t>
+          <t>OCT250401</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2199,7 +2187,7 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>OCT250065</t>
+          <t>OCT250402</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2226,7 +2214,7 @@
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>OCT250066</t>
+          <t>OCT250403</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2253,7 +2241,7 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>OCT250067</t>
+          <t>OCT250404</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2280,7 +2268,7 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>OCT250068</t>
+          <t>OCT250405</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2307,7 +2295,7 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>OCT250069</t>
+          <t>OCT250406</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2334,7 +2322,7 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>OCT250070</t>
+          <t>OCT250407</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2361,7 +2349,7 @@
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>OCT250071</t>
+          <t>OCT250408</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2388,7 +2376,7 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>OCT250072</t>
+          <t>OCT250409</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2415,7 +2403,7 @@
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>OCT250073</t>
+          <t>OCT250410</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2442,7 +2430,7 @@
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>OCT250074</t>
+          <t>OCT250411</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2469,7 +2457,7 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>OCT250075</t>
+          <t>OCT250412</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2496,7 +2484,7 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>OCT250076</t>
+          <t>OCT250413</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2523,7 +2511,7 @@
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>OCT250077</t>
+          <t>OCT250414</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2550,7 +2538,7 @@
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>OCT250078</t>
+          <t>OCT250415</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2577,7 +2565,7 @@
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>OCT250079</t>
+          <t>OCT250416</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2604,7 +2592,7 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>OCT250080</t>
+          <t>OCT250417</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2631,7 +2619,7 @@
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>OCT250081</t>
+          <t>OCT250418</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2658,7 +2646,7 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>OCT250082</t>
+          <t>OCT250419</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2685,7 +2673,7 @@
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>OCT250083</t>
+          <t>OCT250420</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2712,7 +2700,7 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>OCT250084</t>
+          <t>OCT250421</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2739,7 +2727,7 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>OCT250085</t>
+          <t>OCT250422</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2766,7 +2754,7 @@
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>OCT250086</t>
+          <t>OCT250423</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2793,7 +2781,7 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>OCT250087</t>
+          <t>OCT250424</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2820,7 +2808,7 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>OCT250088</t>
+          <t>OCT250425</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2847,7 +2835,7 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>OCT250089</t>
+          <t>OCT250426</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2874,7 +2862,7 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>OCT250090</t>
+          <t>OCT250427</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2901,7 +2889,7 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>OCT250091</t>
+          <t>OCT250428</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2928,7 +2916,7 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>OCT250092</t>
+          <t>OCT250429</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2955,7 +2943,7 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>OCT250093</t>
+          <t>OCT250430</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2982,7 +2970,7 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>OCT250094</t>
+          <t>OCT250431</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3009,7 +2997,7 @@
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>OCT250095</t>
+          <t>OCT250432</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3036,7 +3024,7 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>OCT250096</t>
+          <t>OCT250433</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3063,7 +3051,7 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>OCT250097</t>
+          <t>OCT250434</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3090,7 +3078,7 @@
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>OCT250098</t>
+          <t>OCT250435</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3117,7 +3105,7 @@
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>OCT250099</t>
+          <t>OCT250436</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3144,7 +3132,7 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>OCT250100</t>
+          <t>OCT250437</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3171,7 +3159,7 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>OCT250101</t>
+          <t>OCT250438</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3198,7 +3186,7 @@
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>OCT250102</t>
+          <t>OCT250439</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3225,7 +3213,7 @@
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>OCT250103</t>
+          <t>OCT250440</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3252,7 +3240,7 @@
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>OCT250104</t>
+          <t>OCT250441</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3279,7 +3267,7 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>OCT250105</t>
+          <t>OCT250442</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3306,7 +3294,7 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>OCT250106</t>
+          <t>OCT250443</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3333,7 +3321,7 @@
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>OCT250107</t>
+          <t>OCT250444</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3360,7 +3348,7 @@
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>OCT250108</t>
+          <t>OCT250445</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3387,7 +3375,7 @@
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>OCT250109</t>
+          <t>OCT250446</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3414,7 +3402,7 @@
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>OCT250110</t>
+          <t>OCT250447</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3441,7 +3429,7 @@
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t>OCT250111</t>
+          <t>OCT250448</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3468,7 +3456,7 @@
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>OCT250112</t>
+          <t>OCT250449</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3495,7 +3483,7 @@
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>OCT250113</t>
+          <t>OCT250450</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3522,7 +3510,7 @@
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>OCT250114</t>
+          <t>OCT250451</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3549,7 +3537,7 @@
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>OCT250115</t>
+          <t>OCT250452</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3576,7 +3564,7 @@
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>OCT250116</t>
+          <t>OCT250453</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3603,7 +3591,7 @@
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>OCT250117</t>
+          <t>OCT250454</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3630,7 +3618,7 @@
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>OCT250118</t>
+          <t>OCT250455</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3657,7 +3645,7 @@
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>OCT250119</t>
+          <t>OCT250456</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3684,7 +3672,7 @@
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>OCT250120</t>
+          <t>OCT250457</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3711,7 +3699,7 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>OCT250121</t>
+          <t>OCT250458</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3738,7 +3726,7 @@
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>OCT250122</t>
+          <t>OCT250459</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3765,7 +3753,7 @@
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>OCT250123</t>
+          <t>OCT250460</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3792,7 +3780,7 @@
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>OCT250124</t>
+          <t>OCT250461</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3819,7 +3807,7 @@
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>OCT250125</t>
+          <t>OCT250462</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3846,7 +3834,7 @@
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t>OCT250126</t>
+          <t>OCT250463</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3873,7 +3861,7 @@
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>OCT250127</t>
+          <t>OCT250464</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3900,7 +3888,7 @@
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>OCT250128</t>
+          <t>OCT250465</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3927,7 +3915,7 @@
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t>OCT250129</t>
+          <t>OCT250466</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3954,7 +3942,7 @@
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>OCT250130</t>
+          <t>OCT250467</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3981,7 +3969,7 @@
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>OCT250131</t>
+          <t>OCT250468</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4008,7 +3996,7 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>OCT250132</t>
+          <t>OCT250469</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4035,7 +4023,7 @@
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>OCT250133</t>
+          <t>OCT250470</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4062,7 +4050,7 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>OCT250134</t>
+          <t>OCT250471</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4089,7 +4077,7 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>OCT250135</t>
+          <t>OCT250472</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4116,7 +4104,7 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>OCT250136</t>
+          <t>OCT250473</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4143,7 +4131,7 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>OCT250137</t>
+          <t>OCT250474</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4170,7 +4158,7 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>OCT250138</t>
+          <t>OCT250475</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4197,7 +4185,7 @@
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>OCT250139</t>
+          <t>OCT250476</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4224,7 +4212,7 @@
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>OCT250140</t>
+          <t>OCT250477</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4251,7 +4239,7 @@
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t>OCT250141</t>
+          <t>OCT250478</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4278,7 +4266,7 @@
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t>OCT250142</t>
+          <t>OCT250479</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4305,7 +4293,7 @@
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t>OCT250143</t>
+          <t>OCT250480</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4332,7 +4320,7 @@
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t>OCT250144</t>
+          <t>OCT250481</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4359,7 +4347,7 @@
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>OCT250145</t>
+          <t>OCT250482</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4386,7 +4374,7 @@
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>OCT250146</t>
+          <t>OCT250483</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4413,7 +4401,7 @@
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t>OCT250147</t>
+          <t>OCT250484</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4440,7 +4428,7 @@
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t>OCT250148</t>
+          <t>OCT250485</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4467,7 +4455,7 @@
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t>OCT250149</t>
+          <t>OCT250486</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4494,7 +4482,7 @@
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>OCT250150</t>
+          <t>OCT250487</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4521,7 +4509,7 @@
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>OCT250151</t>
+          <t>OCT250488</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4548,7 +4536,7 @@
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>OCT250152</t>
+          <t>OCT250489</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4575,7 +4563,7 @@
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>OCT250153</t>
+          <t>OCT250490</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4602,7 +4590,7 @@
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>OCT250154</t>
+          <t>OCT250491</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4629,7 +4617,7 @@
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>OCT250155</t>
+          <t>OCT250492</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4656,7 +4644,7 @@
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>OCT250156</t>
+          <t>OCT250493</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4683,7 +4671,7 @@
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>OCT250157</t>
+          <t>OCT250494</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4710,7 +4698,7 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>OCT250158</t>
+          <t>OCT250495</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4737,7 +4725,7 @@
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>OCT250159</t>
+          <t>OCT250496</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4764,7 +4752,7 @@
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>OCT250160</t>
+          <t>OCT250497</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4791,7 +4779,7 @@
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>OCT250161</t>
+          <t>OCT250498</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4818,7 +4806,7 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>OCT250162</t>
+          <t>OCT250499</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4845,7 +4833,7 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>OCT250163</t>
+          <t>OCT250500</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4872,7 +4860,7 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>OCT250164</t>
+          <t>OCT250501</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4899,7 +4887,7 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>OCT250165</t>
+          <t>OCT250502</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4926,7 +4914,7 @@
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>OCT250166</t>
+          <t>OCT250503</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4953,7 +4941,7 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>OCT250167</t>
+          <t>OCT250504</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4980,7 +4968,7 @@
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t>OCT250168</t>
+          <t>OCT250505</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5007,7 +4995,7 @@
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>OCT250169</t>
+          <t>OCT250506</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5034,7 +5022,7 @@
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t>OCT250170</t>
+          <t>OCT250507</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5061,7 +5049,7 @@
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t>OCT250171</t>
+          <t>OCT250508</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5088,7 +5076,7 @@
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t>OCT250172</t>
+          <t>OCT250509</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5115,7 +5103,7 @@
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t>OCT250173</t>
+          <t>OCT250510</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5142,7 +5130,7 @@
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t>OCT250174</t>
+          <t>OCT250511</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5169,7 +5157,7 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>OCT250175</t>
+          <t>OCT250512</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5196,7 +5184,7 @@
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>OCT250176</t>
+          <t>OCT250513</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5223,7 +5211,7 @@
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>OCT250177</t>
+          <t>OCT250514</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5250,7 +5238,7 @@
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t>OCT250178</t>
+          <t>OCT250515</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5277,7 +5265,7 @@
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t>OCT250179</t>
+          <t>OCT250516</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5304,7 +5292,7 @@
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t>OCT250180</t>
+          <t>OCT250517</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5331,7 +5319,7 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>OCT250181</t>
+          <t>OCT250518</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5358,7 +5346,7 @@
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t>OCT250182</t>
+          <t>OCT250519</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5385,7 +5373,7 @@
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t>OCT250183</t>
+          <t>OCT250520</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5412,7 +5400,7 @@
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t>OCT250184</t>
+          <t>OCT250521</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5439,7 +5427,7 @@
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t>OCT250185</t>
+          <t>OCT250522</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5466,7 +5454,7 @@
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t>OCT250186</t>
+          <t>OCT250523</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5493,7 +5481,7 @@
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t>OCT250187</t>
+          <t>OCT250524</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5520,7 +5508,7 @@
     <row r="189">
       <c r="B189" t="inlineStr">
         <is>
-          <t>OCT250188</t>
+          <t>OCT250525</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5547,7 +5535,7 @@
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
-          <t>OCT250189</t>
+          <t>OCT250526</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5574,7 +5562,7 @@
     <row r="191">
       <c r="B191" t="inlineStr">
         <is>
-          <t>OCT250190</t>
+          <t>OCT250527</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5601,7 +5589,7 @@
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t>OCT250191</t>
+          <t>OCT250528</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5628,7 +5616,7 @@
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t>OCT250192</t>
+          <t>OCT250529</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5655,7 +5643,7 @@
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t>OCT250193</t>
+          <t>OCT250530</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5682,7 +5670,7 @@
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t>OCT250194</t>
+          <t>OCT250531</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5709,7 +5697,7 @@
     <row r="196">
       <c r="B196" t="inlineStr">
         <is>
-          <t>OCT250195</t>
+          <t>OCT250532</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5736,7 +5724,7 @@
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
-          <t>OCT250196</t>
+          <t>OCT250533</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5763,7 +5751,7 @@
     <row r="198">
       <c r="B198" t="inlineStr">
         <is>
-          <t>OCT250197</t>
+          <t>OCT250534</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5790,7 +5778,7 @@
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t>OCT250198</t>
+          <t>OCT250535</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5817,7 +5805,7 @@
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t>OCT250199</t>
+          <t>OCT250536</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5844,7 +5832,7 @@
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t>OCT250200</t>
+          <t>OCT250537</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5871,7 +5859,7 @@
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t>OCT250201</t>
+          <t>OCT250538</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5898,7 +5886,7 @@
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t>OCT250202</t>
+          <t>OCT250539</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5925,7 +5913,7 @@
     <row r="204">
       <c r="B204" t="inlineStr">
         <is>
-          <t>OCT250203</t>
+          <t>OCT250540</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5952,7 +5940,7 @@
     <row r="205">
       <c r="B205" t="inlineStr">
         <is>
-          <t>OCT250204</t>
+          <t>OCT250541</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5979,7 +5967,7 @@
     <row r="206">
       <c r="B206" t="inlineStr">
         <is>
-          <t>OCT250205</t>
+          <t>OCT250542</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6006,7 +5994,7 @@
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
-          <t>OCT250206</t>
+          <t>OCT250543</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6033,7 +6021,7 @@
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t>OCT250207</t>
+          <t>OCT250544</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6060,7 +6048,7 @@
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t>OCT250208</t>
+          <t>OCT250545</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6087,7 +6075,7 @@
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t>OCT250209</t>
+          <t>OCT250546</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6114,7 +6102,7 @@
     <row r="211">
       <c r="B211" t="inlineStr">
         <is>
-          <t>OCT250210</t>
+          <t>OCT250547</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6141,7 +6129,7 @@
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t>OCT250211</t>
+          <t>OCT250548</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6168,7 +6156,7 @@
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t>OCT250212</t>
+          <t>OCT250549</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6195,7 +6183,7 @@
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t>OCT250213</t>
+          <t>OCT250550</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6222,7 +6210,7 @@
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t>OCT250214</t>
+          <t>OCT250551</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6249,7 +6237,7 @@
     <row r="216">
       <c r="B216" t="inlineStr">
         <is>
-          <t>OCT250215</t>
+          <t>OCT250552</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6276,7 +6264,7 @@
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
-          <t>OCT250216</t>
+          <t>OCT250553</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6303,7 +6291,7 @@
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t>OCT250217</t>
+          <t>OCT250554</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6330,7 +6318,7 @@
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t>OCT250218</t>
+          <t>OCT250555</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6357,7 +6345,7 @@
     <row r="220">
       <c r="B220" t="inlineStr">
         <is>
-          <t>OCT250219</t>
+          <t>OCT250556</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6384,7 +6372,7 @@
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t>OCT250220</t>
+          <t>OCT250557</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6411,7 +6399,7 @@
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t>OCT250221</t>
+          <t>OCT250558</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6438,7 +6426,7 @@
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t>OCT250222</t>
+          <t>OCT250559</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6465,7 +6453,7 @@
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t>OCT250223</t>
+          <t>OCT250560</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6492,7 +6480,7 @@
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>OCT250224</t>
+          <t>OCT250561</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6519,7 +6507,7 @@
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t>OCT250225</t>
+          <t>OCT250562</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6546,7 +6534,7 @@
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
-          <t>OCT250226</t>
+          <t>OCT250563</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6573,7 +6561,7 @@
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t>OCT250227</t>
+          <t>OCT250564</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6600,7 +6588,7 @@
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t>OCT250228</t>
+          <t>OCT250565</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6627,7 +6615,7 @@
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t>OCT250229</t>
+          <t>OCT250566</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6654,7 +6642,7 @@
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t>OCT250230</t>
+          <t>OCT250567</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6681,7 +6669,7 @@
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t>OCT250231</t>
+          <t>OCT250568</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6708,7 +6696,7 @@
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t>OCT250232</t>
+          <t>OCT250569</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6735,7 +6723,7 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t>OCT250233</t>
+          <t>OCT250570</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6762,7 +6750,7 @@
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t>OCT250234</t>
+          <t>OCT250571</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6789,7 +6777,7 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t>OCT250235</t>
+          <t>OCT250572</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6816,7 +6804,7 @@
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t>OCT250236</t>
+          <t>OCT250573</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6843,7 +6831,7 @@
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t>OCT250237</t>
+          <t>OCT250574</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6870,7 +6858,7 @@
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t>OCT250238</t>
+          <t>OCT250575</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6897,7 +6885,7 @@
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t>OCT250239</t>
+          <t>OCT250576</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6924,7 +6912,7 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
-          <t>OCT250240</t>
+          <t>OCT250577</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6951,7 +6939,7 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t>OCT250241</t>
+          <t>OCT250578</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6978,7 +6966,7 @@
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t>OCT250242</t>
+          <t>OCT250579</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7005,7 +6993,7 @@
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t>OCT250243</t>
+          <t>OCT250580</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7032,7 +7020,7 @@
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t>OCT250244</t>
+          <t>OCT250581</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7059,7 +7047,7 @@
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t>OCT250245</t>
+          <t>OCT250582</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7086,7 +7074,7 @@
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t>OCT250246</t>
+          <t>OCT250583</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7113,7 +7101,7 @@
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>OCT250247</t>
+          <t>OCT250584</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7140,7 +7128,7 @@
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t>OCT250248</t>
+          <t>OCT250585</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7167,7 +7155,7 @@
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t>OCT250249</t>
+          <t>OCT250586</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7194,7 +7182,7 @@
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t>OCT250250</t>
+          <t>OCT250587</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7221,7 +7209,7 @@
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t>OCT250251</t>
+          <t>OCT250588</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7248,7 +7236,7 @@
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
-          <t>OCT250252</t>
+          <t>OCT250589</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7275,7 +7263,7 @@
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
-          <t>OCT250253</t>
+          <t>OCT250590</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7302,7 +7290,7 @@
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
-          <t>OCT250254</t>
+          <t>OCT250591</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7329,7 +7317,7 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t>OCT250255</t>
+          <t>OCT250592</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7356,7 +7344,7 @@
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
-          <t>OCT250256</t>
+          <t>OCT250593</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7383,7 +7371,7 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
-          <t>OCT250257</t>
+          <t>OCT250594</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7410,7 +7398,7 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>OCT250258</t>
+          <t>OCT250595</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7437,7 +7425,7 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t>OCT250259</t>
+          <t>OCT250596</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7464,7 +7452,7 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t>OCT250260</t>
+          <t>OCT250597</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7491,7 +7479,7 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t>OCT250261</t>
+          <t>OCT250598</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7518,7 +7506,7 @@
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t>OCT250262</t>
+          <t>OCT250599</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7545,7 +7533,7 @@
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
-          <t>OCT250263</t>
+          <t>OCT250600</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7572,7 +7560,7 @@
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t>OCT250264</t>
+          <t>OCT250601</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7599,7 +7587,7 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>OCT250265</t>
+          <t>OCT250602</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7626,7 +7614,7 @@
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t>OCT250266</t>
+          <t>OCT250603</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7653,7 +7641,7 @@
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t>OCT250267</t>
+          <t>OCT250604</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7680,7 +7668,7 @@
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t>OCT250268</t>
+          <t>OCT250605</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7707,7 +7695,7 @@
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>OCT250269</t>
+          <t>OCT250606</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7734,7 +7722,7 @@
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>OCT250270</t>
+          <t>OCT250607</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7761,7 +7749,7 @@
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>OCT250271</t>
+          <t>OCT250608</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7788,7 +7776,7 @@
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>OCT250272</t>
+          <t>OCT250609</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7815,7 +7803,7 @@
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>OCT250273</t>
+          <t>OCT250610</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7842,7 +7830,7 @@
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>OCT250274</t>
+          <t>OCT250611</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7869,7 +7857,7 @@
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>OCT250275</t>
+          <t>OCT250612</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7896,7 +7884,7 @@
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>OCT250276</t>
+          <t>OCT250613</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7923,7 +7911,7 @@
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>OCT250277</t>
+          <t>OCT250614</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7950,7 +7938,7 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>OCT250278</t>
+          <t>OCT250615</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7977,7 +7965,7 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>OCT250279</t>
+          <t>OCT250616</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8004,7 +7992,7 @@
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>OCT250280</t>
+          <t>OCT250617</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8031,7 +8019,7 @@
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>OCT250281</t>
+          <t>OCT250618</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8058,7 +8046,7 @@
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>OCT250282</t>
+          <t>OCT250619</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8085,7 +8073,7 @@
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>OCT250283</t>
+          <t>OCT250620</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8112,7 +8100,7 @@
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>OCT250284</t>
+          <t>OCT250621</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8139,7 +8127,7 @@
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>OCT250285</t>
+          <t>OCT250622</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8166,7 +8154,7 @@
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
-          <t>OCT250286</t>
+          <t>OCT250623</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8193,7 +8181,7 @@
     <row r="288">
       <c r="B288" t="inlineStr">
         <is>
-          <t>OCT250287</t>
+          <t>OCT250624</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8220,7 +8208,7 @@
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>OCT250288</t>
+          <t>OCT250625</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8247,7 +8235,7 @@
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>OCT250289</t>
+          <t>OCT250626</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8274,7 +8262,7 @@
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>OCT250290</t>
+          <t>OCT250627</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8301,7 +8289,7 @@
     <row r="292">
       <c r="B292" t="inlineStr">
         <is>
-          <t>OCT250291</t>
+          <t>OCT250628</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8328,7 +8316,7 @@
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>OCT250292</t>
+          <t>OCT250629</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8355,7 +8343,7 @@
     <row r="294">
       <c r="B294" t="inlineStr">
         <is>
-          <t>OCT250293</t>
+          <t>OCT250630</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8382,7 +8370,7 @@
     <row r="295">
       <c r="B295" t="inlineStr">
         <is>
-          <t>OCT250294</t>
+          <t>OCT250631</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8409,7 +8397,7 @@
     <row r="296">
       <c r="B296" t="inlineStr">
         <is>
-          <t>OCT250295</t>
+          <t>OCT250632</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8436,7 +8424,7 @@
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
-          <t>OCT250296</t>
+          <t>OCT250633</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8463,7 +8451,7 @@
     <row r="298">
       <c r="B298" t="inlineStr">
         <is>
-          <t>OCT250297</t>
+          <t>OCT250634</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8490,7 +8478,7 @@
     <row r="299">
       <c r="B299" t="inlineStr">
         <is>
-          <t>OCT250298</t>
+          <t>OCT250635</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8517,7 +8505,7 @@
     <row r="300">
       <c r="B300" t="inlineStr">
         <is>
-          <t>OCT250299</t>
+          <t>OCT250636</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8544,7 +8532,7 @@
     <row r="301">
       <c r="B301" t="inlineStr">
         <is>
-          <t>OCT250300</t>
+          <t>OCT250637</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8571,7 +8559,7 @@
     <row r="302">
       <c r="B302" t="inlineStr">
         <is>
-          <t>OCT250301</t>
+          <t>OCT250638</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8598,7 +8586,7 @@
     <row r="303">
       <c r="B303" t="inlineStr">
         <is>
-          <t>OCT250302</t>
+          <t>OCT250639</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8625,7 +8613,7 @@
     <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>OCT250303</t>
+          <t>OCT250640</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8652,7 +8640,7 @@
     <row r="305">
       <c r="B305" t="inlineStr">
         <is>
-          <t>OCT250304</t>
+          <t>OCT250641</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8679,7 +8667,7 @@
     <row r="306">
       <c r="B306" t="inlineStr">
         <is>
-          <t>OCT250305</t>
+          <t>OCT250642</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8706,7 +8694,7 @@
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
-          <t>OCT250306</t>
+          <t>OCT250643</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8733,7 +8721,7 @@
     <row r="308">
       <c r="B308" t="inlineStr">
         <is>
-          <t>OCT250307</t>
+          <t>OCT250644</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8760,7 +8748,7 @@
     <row r="309">
       <c r="B309" t="inlineStr">
         <is>
-          <t>OCT250308</t>
+          <t>OCT250645</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8787,7 +8775,7 @@
     <row r="310">
       <c r="B310" t="inlineStr">
         <is>
-          <t>OCT250309</t>
+          <t>OCT250646</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8814,7 +8802,7 @@
     <row r="311">
       <c r="B311" t="inlineStr">
         <is>
-          <t>OCT250310</t>
+          <t>OCT250647</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8841,7 +8829,7 @@
     <row r="312">
       <c r="B312" t="inlineStr">
         <is>
-          <t>OCT250311</t>
+          <t>OCT250648</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8868,7 +8856,7 @@
     <row r="313">
       <c r="B313" t="inlineStr">
         <is>
-          <t>OCT250312</t>
+          <t>OCT250649</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8895,7 +8883,7 @@
     <row r="314">
       <c r="B314" t="inlineStr">
         <is>
-          <t>OCT250313</t>
+          <t>OCT250650</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8922,7 +8910,7 @@
     <row r="315">
       <c r="B315" t="inlineStr">
         <is>
-          <t>OCT250314</t>
+          <t>OCT250651</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8949,7 +8937,7 @@
     <row r="316">
       <c r="B316" t="inlineStr">
         <is>
-          <t>OCT250315</t>
+          <t>OCT250652</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8976,7 +8964,7 @@
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
-          <t>OCT250316</t>
+          <t>OCT250653</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9003,7 +8991,7 @@
     <row r="318">
       <c r="B318" t="inlineStr">
         <is>
-          <t>OCT250317</t>
+          <t>OCT250654</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9030,7 +9018,7 @@
     <row r="319">
       <c r="B319" t="inlineStr">
         <is>
-          <t>OCT250318</t>
+          <t>OCT250655</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9057,7 +9045,7 @@
     <row r="320">
       <c r="B320" t="inlineStr">
         <is>
-          <t>OCT250319</t>
+          <t>OCT250656</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9084,7 +9072,7 @@
     <row r="321">
       <c r="B321" t="inlineStr">
         <is>
-          <t>OCT250320</t>
+          <t>OCT250657</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9111,7 +9099,7 @@
     <row r="322">
       <c r="B322" t="inlineStr">
         <is>
-          <t>OCT250321</t>
+          <t>OCT250658</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9138,7 +9126,7 @@
     <row r="323">
       <c r="B323" t="inlineStr">
         <is>
-          <t>OCT250322</t>
+          <t>OCT250659</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9165,7 +9153,7 @@
     <row r="324">
       <c r="B324" t="inlineStr">
         <is>
-          <t>OCT250323</t>
+          <t>OCT250660</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9192,7 +9180,7 @@
     <row r="325">
       <c r="B325" t="inlineStr">
         <is>
-          <t>OCT250324</t>
+          <t>OCT250661</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9219,7 +9207,7 @@
     <row r="326">
       <c r="B326" t="inlineStr">
         <is>
-          <t>OCT250325</t>
+          <t>OCT250662</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9246,7 +9234,7 @@
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
-          <t>OCT250326</t>
+          <t>OCT250663</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9273,7 +9261,7 @@
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>OCT250327</t>
+          <t>OCT250664</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9300,7 +9288,7 @@
     <row r="329">
       <c r="B329" t="inlineStr">
         <is>
-          <t>OCT250328</t>
+          <t>OCT250665</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9327,7 +9315,7 @@
     <row r="330">
       <c r="B330" t="inlineStr">
         <is>
-          <t>OCT250329</t>
+          <t>OCT250666</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9354,7 +9342,7 @@
     <row r="331">
       <c r="B331" t="inlineStr">
         <is>
-          <t>OCT250330</t>
+          <t>OCT250667</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9381,7 +9369,7 @@
     <row r="332">
       <c r="B332" t="inlineStr">
         <is>
-          <t>OCT250331</t>
+          <t>OCT250668</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9408,7 +9396,7 @@
     <row r="333">
       <c r="B333" t="inlineStr">
         <is>
-          <t>OCT250332</t>
+          <t>OCT250669</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9435,7 +9423,7 @@
     <row r="334">
       <c r="B334" t="inlineStr">
         <is>
-          <t>OCT250333</t>
+          <t>OCT250670</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -9462,7 +9450,7 @@
     <row r="335">
       <c r="B335" t="inlineStr">
         <is>
-          <t>OCT250334</t>
+          <t>OCT250671</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -9489,7 +9477,7 @@
     <row r="336">
       <c r="B336" t="inlineStr">
         <is>
-          <t>OCT250335</t>
+          <t>OCT250672</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -9516,7 +9504,7 @@
     <row r="337">
       <c r="B337" t="inlineStr">
         <is>
-          <t>OCT250336</t>
+          <t>OCT250673</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -9543,7 +9531,7 @@
     <row r="338">
       <c r="B338" t="inlineStr">
         <is>
-          <t>OCT250337</t>
+          <t>OCT250674</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -9570,7 +9558,7 @@
     <row r="339">
       <c r="B339" t="inlineStr">
         <is>
-          <t>OCT250338</t>
+          <t>OCT250675</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9597,7 +9585,7 @@
     <row r="340">
       <c r="B340" t="inlineStr">
         <is>
-          <t>OCT250339</t>
+          <t>OCT250676</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -9624,7 +9612,7 @@
     <row r="341">
       <c r="B341" t="inlineStr">
         <is>
-          <t>OCT250340</t>
+          <t>OCT250677</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -9651,7 +9639,7 @@
     <row r="342">
       <c r="B342" t="inlineStr">
         <is>
-          <t>OCT250341</t>
+          <t>OCT250678</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -9678,7 +9666,7 @@
     <row r="343">
       <c r="B343" t="inlineStr">
         <is>
-          <t>OCT250342</t>
+          <t>OCT250679</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -9705,7 +9693,7 @@
     <row r="344">
       <c r="B344" t="inlineStr">
         <is>
-          <t>OCT250343</t>
+          <t>OCT250680</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -9732,7 +9720,7 @@
     <row r="345">
       <c r="B345" t="inlineStr">
         <is>
-          <t>OCT250344</t>
+          <t>OCT250681</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -9759,7 +9747,7 @@
     <row r="346">
       <c r="B346" t="inlineStr">
         <is>
-          <t>OCT250345</t>
+          <t>OCT250682</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -9786,7 +9774,7 @@
     <row r="347">
       <c r="B347" t="inlineStr">
         <is>
-          <t>OCT250346</t>
+          <t>OCT250683</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -9813,7 +9801,7 @@
     <row r="348">
       <c r="B348" t="inlineStr">
         <is>
-          <t>OCT250347</t>
+          <t>OCT250684</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -9840,7 +9828,7 @@
     <row r="349">
       <c r="B349" t="inlineStr">
         <is>
-          <t>OCT250348</t>
+          <t>OCT250685</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9867,7 +9855,7 @@
     <row r="350">
       <c r="B350" t="inlineStr">
         <is>
-          <t>OCT250349</t>
+          <t>OCT250686</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -9894,7 +9882,7 @@
     <row r="351">
       <c r="B351" t="inlineStr">
         <is>
-          <t>OCT250350</t>
+          <t>OCT250687</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9921,7 +9909,7 @@
     <row r="352">
       <c r="B352" t="inlineStr">
         <is>
-          <t>OCT250351</t>
+          <t>OCT250688</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9948,7 +9936,7 @@
     <row r="353">
       <c r="B353" t="inlineStr">
         <is>
-          <t>OCT250352</t>
+          <t>OCT250689</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9975,7 +9963,7 @@
     <row r="354">
       <c r="B354" t="inlineStr">
         <is>
-          <t>OCT250353</t>
+          <t>OCT250690</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10002,7 +9990,7 @@
     <row r="355">
       <c r="B355" t="inlineStr">
         <is>
-          <t>OCT250354</t>
+          <t>OCT250691</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10029,7 +10017,7 @@
     <row r="356">
       <c r="B356" t="inlineStr">
         <is>
-          <t>OCT250355</t>
+          <t>OCT250692</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10056,7 +10044,7 @@
     <row r="357">
       <c r="B357" t="inlineStr">
         <is>
-          <t>OCT250356</t>
+          <t>OCT250693</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10083,7 +10071,7 @@
     <row r="358">
       <c r="B358" t="inlineStr">
         <is>
-          <t>OCT250357</t>
+          <t>OCT250694</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10110,7 +10098,7 @@
     <row r="359">
       <c r="B359" t="inlineStr">
         <is>
-          <t>OCT250358</t>
+          <t>OCT250695</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10137,7 +10125,7 @@
     <row r="360">
       <c r="B360" t="inlineStr">
         <is>
-          <t>OCT250359</t>
+          <t>OCT250696</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10164,7 +10152,7 @@
     <row r="361">
       <c r="B361" t="inlineStr">
         <is>
-          <t>OCT250360</t>
+          <t>OCT250697</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10191,7 +10179,7 @@
     <row r="362">
       <c r="B362" t="inlineStr">
         <is>
-          <t>OCT250361</t>
+          <t>OCT250698</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10218,7 +10206,7 @@
     <row r="363">
       <c r="B363" t="inlineStr">
         <is>
-          <t>OCT250362</t>
+          <t>OCT250699</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10245,7 +10233,7 @@
     <row r="364">
       <c r="B364" t="inlineStr">
         <is>
-          <t>OCT250363</t>
+          <t>OCT250700</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10272,7 +10260,7 @@
     <row r="365">
       <c r="B365" t="inlineStr">
         <is>
-          <t>OCT250364</t>
+          <t>OCT250701</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10299,7 +10287,7 @@
     <row r="366">
       <c r="B366" t="inlineStr">
         <is>
-          <t>OCT250365</t>
+          <t>OCT250702</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10326,7 +10314,7 @@
     <row r="367">
       <c r="B367" t="inlineStr">
         <is>
-          <t>OCT250366</t>
+          <t>OCT250703</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10353,7 +10341,7 @@
     <row r="368">
       <c r="B368" t="inlineStr">
         <is>
-          <t>OCT250367</t>
+          <t>OCT250704</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10380,7 +10368,7 @@
     <row r="369">
       <c r="B369" t="inlineStr">
         <is>
-          <t>OCT250368</t>
+          <t>OCT250705</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10407,7 +10395,7 @@
     <row r="370">
       <c r="B370" t="inlineStr">
         <is>
-          <t>OCT250369</t>
+          <t>OCT250706</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10434,7 +10422,7 @@
     <row r="371">
       <c r="B371" t="inlineStr">
         <is>
-          <t>OCT250370</t>
+          <t>OCT250707</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10461,7 +10449,7 @@
     <row r="372">
       <c r="B372" t="inlineStr">
         <is>
-          <t>OCT250371</t>
+          <t>OCT250708</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10488,7 +10476,7 @@
     <row r="373">
       <c r="B373" t="inlineStr">
         <is>
-          <t>OCT250372</t>
+          <t>OCT250709</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10515,7 +10503,7 @@
     <row r="374">
       <c r="B374" t="inlineStr">
         <is>
-          <t>OCT250373</t>
+          <t>OCT250710</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10542,7 +10530,7 @@
     <row r="375">
       <c r="B375" t="inlineStr">
         <is>
-          <t>OCT250374</t>
+          <t>OCT250711</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10569,7 +10557,7 @@
     <row r="376">
       <c r="B376" t="inlineStr">
         <is>
-          <t>OCT250375</t>
+          <t>OCT250712</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10596,7 +10584,7 @@
     <row r="377">
       <c r="B377" t="inlineStr">
         <is>
-          <t>OCT250376</t>
+          <t>OCT250713</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10623,7 +10611,7 @@
     <row r="378">
       <c r="B378" t="inlineStr">
         <is>
-          <t>OCT250377</t>
+          <t>OCT250714</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -10650,7 +10638,7 @@
     <row r="379">
       <c r="B379" t="inlineStr">
         <is>
-          <t>OCT250378</t>
+          <t>OCT250715</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10677,7 +10665,7 @@
     <row r="380">
       <c r="B380" t="inlineStr">
         <is>
-          <t>OCT250379</t>
+          <t>OCT250716</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10704,7 +10692,7 @@
     <row r="381">
       <c r="B381" t="inlineStr">
         <is>
-          <t>OCT250380</t>
+          <t>OCT250717</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10731,7 +10719,7 @@
     <row r="382">
       <c r="B382" t="inlineStr">
         <is>
-          <t>OCT250381</t>
+          <t>OCT250718</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10758,7 +10746,7 @@
     <row r="383">
       <c r="B383" t="inlineStr">
         <is>
-          <t>OCT250382</t>
+          <t>OCT250719</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10785,7 +10773,7 @@
     <row r="384">
       <c r="B384" t="inlineStr">
         <is>
-          <t>OCT250383</t>
+          <t>OCT250720</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10812,7 +10800,7 @@
     <row r="385">
       <c r="B385" t="inlineStr">
         <is>
-          <t>OCT250384</t>
+          <t>OCT250721</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10839,7 +10827,7 @@
     <row r="386">
       <c r="B386" t="inlineStr">
         <is>
-          <t>OCT250385</t>
+          <t>OCT250722</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10866,7 +10854,7 @@
     <row r="387">
       <c r="B387" t="inlineStr">
         <is>
-          <t>OCT250386</t>
+          <t>OCT250723</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -10893,7 +10881,7 @@
     <row r="388">
       <c r="B388" t="inlineStr">
         <is>
-          <t>OCT250387</t>
+          <t>OCT250724</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10920,7 +10908,7 @@
     <row r="389">
       <c r="B389" t="inlineStr">
         <is>
-          <t>OCT250388</t>
+          <t>OCT250725</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10947,7 +10935,7 @@
     <row r="390">
       <c r="B390" t="inlineStr">
         <is>
-          <t>OCT250389</t>
+          <t>OCT250726</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10974,7 +10962,7 @@
     <row r="391">
       <c r="B391" t="inlineStr">
         <is>
-          <t>OCT250390</t>
+          <t>OCT250727</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11001,7 +10989,7 @@
     <row r="392">
       <c r="B392" t="inlineStr">
         <is>
-          <t>OCT250391</t>
+          <t>OCT250728</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11028,7 +11016,7 @@
     <row r="393">
       <c r="B393" t="inlineStr">
         <is>
-          <t>OCT250392</t>
+          <t>OCT250729</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11055,7 +11043,7 @@
     <row r="394">
       <c r="B394" t="inlineStr">
         <is>
-          <t>OCT250393</t>
+          <t>OCT250730</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11082,7 +11070,7 @@
     <row r="395">
       <c r="B395" t="inlineStr">
         <is>
-          <t>OCT250394</t>
+          <t>OCT250731</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11109,7 +11097,7 @@
     <row r="396">
       <c r="B396" t="inlineStr">
         <is>
-          <t>OCT250395</t>
+          <t>OCT250732</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11136,7 +11124,7 @@
     <row r="397">
       <c r="B397" t="inlineStr">
         <is>
-          <t>OCT250396</t>
+          <t>OCT250733</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11163,7 +11151,7 @@
     <row r="398">
       <c r="B398" t="inlineStr">
         <is>
-          <t>OCT250397</t>
+          <t>OCT250734</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11190,7 +11178,7 @@
     <row r="399">
       <c r="B399" t="inlineStr">
         <is>
-          <t>OCT250398</t>
+          <t>OCT250735</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11217,7 +11205,7 @@
     <row r="400">
       <c r="B400" t="inlineStr">
         <is>
-          <t>OCT250399</t>
+          <t>OCT250736</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11244,7 +11232,7 @@
     <row r="401">
       <c r="B401" t="inlineStr">
         <is>
-          <t>OCT250400</t>
+          <t>OCT250737</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11271,7 +11259,7 @@
     <row r="402">
       <c r="B402" t="inlineStr">
         <is>
-          <t>OCT250401</t>
+          <t>OCT250738</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11298,7 +11286,7 @@
     <row r="403">
       <c r="B403" t="inlineStr">
         <is>
-          <t>OCT250402</t>
+          <t>OCT250739</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -11325,7 +11313,7 @@
     <row r="404">
       <c r="B404" t="inlineStr">
         <is>
-          <t>OCT250403</t>
+          <t>OCT250740</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -11352,7 +11340,7 @@
     <row r="405">
       <c r="B405" t="inlineStr">
         <is>
-          <t>OCT250404</t>
+          <t>OCT250741</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -11379,7 +11367,7 @@
     <row r="406">
       <c r="B406" t="inlineStr">
         <is>
-          <t>OCT250405</t>
+          <t>OCT250742</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -11406,7 +11394,7 @@
     <row r="407">
       <c r="B407" t="inlineStr">
         <is>
-          <t>OCT250406</t>
+          <t>OCT250743</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11433,7 +11421,7 @@
     <row r="408">
       <c r="B408" t="inlineStr">
         <is>
-          <t>OCT250407</t>
+          <t>OCT250744</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -11460,7 +11448,7 @@
     <row r="409">
       <c r="B409" t="inlineStr">
         <is>
-          <t>OCT250408</t>
+          <t>OCT250745</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11487,7 +11475,7 @@
     <row r="410">
       <c r="B410" t="inlineStr">
         <is>
-          <t>OCT250409</t>
+          <t>OCT250746</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -11514,7 +11502,7 @@
     <row r="411">
       <c r="B411" t="inlineStr">
         <is>
-          <t>OCT250410</t>
+          <t>OCT250747</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -11541,7 +11529,7 @@
     <row r="412">
       <c r="B412" t="inlineStr">
         <is>
-          <t>OCT250411</t>
+          <t>OCT250748</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11568,7 +11556,7 @@
     <row r="413">
       <c r="B413" t="inlineStr">
         <is>
-          <t>OCT250412</t>
+          <t>OCT250749</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -11595,7 +11583,7 @@
     <row r="414">
       <c r="B414" t="inlineStr">
         <is>
-          <t>OCT250413</t>
+          <t>OCT250750</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -11622,7 +11610,7 @@
     <row r="415">
       <c r="B415" t="inlineStr">
         <is>
-          <t>OCT250414</t>
+          <t>OCT250751</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -11649,7 +11637,7 @@
     <row r="416">
       <c r="B416" t="inlineStr">
         <is>
-          <t>OCT250415</t>
+          <t>OCT250752</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -11676,7 +11664,7 @@
     <row r="417">
       <c r="B417" t="inlineStr">
         <is>
-          <t>OCT250416</t>
+          <t>OCT250753</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11703,7 +11691,7 @@
     <row r="418">
       <c r="B418" t="inlineStr">
         <is>
-          <t>OCT250417</t>
+          <t>OCT250754</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11730,7 +11718,7 @@
     <row r="419">
       <c r="B419" t="inlineStr">
         <is>
-          <t>OCT250418</t>
+          <t>OCT250755</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -11757,7 +11745,7 @@
     <row r="420">
       <c r="B420" t="inlineStr">
         <is>
-          <t>OCT250419</t>
+          <t>OCT250756</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11784,7 +11772,7 @@
     <row r="421">
       <c r="B421" t="inlineStr">
         <is>
-          <t>OCT250420</t>
+          <t>OCT250757</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11811,7 +11799,7 @@
     <row r="422">
       <c r="B422" t="inlineStr">
         <is>
-          <t>OCT250421</t>
+          <t>OCT250758</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11838,7 +11826,7 @@
     <row r="423">
       <c r="B423" t="inlineStr">
         <is>
-          <t>OCT250422</t>
+          <t>OCT250759</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11865,7 +11853,7 @@
     <row r="424">
       <c r="B424" t="inlineStr">
         <is>
-          <t>OCT250423</t>
+          <t>OCT250760</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11892,7 +11880,7 @@
     <row r="425">
       <c r="B425" t="inlineStr">
         <is>
-          <t>OCT250424</t>
+          <t>OCT250761</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11919,7 +11907,7 @@
     <row r="426">
       <c r="B426" t="inlineStr">
         <is>
-          <t>OCT250425</t>
+          <t>OCT250762</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11946,7 +11934,7 @@
     <row r="427">
       <c r="B427" t="inlineStr">
         <is>
-          <t>OCT250426</t>
+          <t>OCT250763</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11973,7 +11961,7 @@
     <row r="428">
       <c r="B428" t="inlineStr">
         <is>
-          <t>OCT250427</t>
+          <t>OCT250764</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12000,7 +11988,7 @@
     <row r="429">
       <c r="B429" t="inlineStr">
         <is>
-          <t>OCT250428</t>
+          <t>OCT250765</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -12027,7 +12015,7 @@
     <row r="430">
       <c r="B430" t="inlineStr">
         <is>
-          <t>OCT250429</t>
+          <t>OCT250766</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12054,7 +12042,7 @@
     <row r="431">
       <c r="B431" t="inlineStr">
         <is>
-          <t>OCT250430</t>
+          <t>OCT250767</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12081,7 +12069,7 @@
     <row r="432">
       <c r="B432" t="inlineStr">
         <is>
-          <t>OCT250431</t>
+          <t>OCT250768</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12108,7 +12096,7 @@
     <row r="433">
       <c r="B433" t="inlineStr">
         <is>
-          <t>OCT250432</t>
+          <t>OCT250769</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12135,7 +12123,7 @@
     <row r="434">
       <c r="B434" t="inlineStr">
         <is>
-          <t>OCT250433</t>
+          <t>OCT250770</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12162,7 +12150,7 @@
     <row r="435">
       <c r="B435" t="inlineStr">
         <is>
-          <t>OCT250434</t>
+          <t>OCT250771</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12189,7 +12177,7 @@
     <row r="436">
       <c r="B436" t="inlineStr">
         <is>
-          <t>OCT250435</t>
+          <t>OCT250772</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12216,7 +12204,7 @@
     <row r="437">
       <c r="B437" t="inlineStr">
         <is>
-          <t>OCT250436</t>
+          <t>OCT250773</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -12243,7 +12231,7 @@
     <row r="438">
       <c r="B438" t="inlineStr">
         <is>
-          <t>OCT250437</t>
+          <t>OCT250774</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12270,7 +12258,7 @@
     <row r="439">
       <c r="B439" t="inlineStr">
         <is>
-          <t>OCT250438</t>
+          <t>OCT250775</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12297,7 +12285,7 @@
     <row r="440">
       <c r="B440" t="inlineStr">
         <is>
-          <t>OCT250439</t>
+          <t>OCT250776</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -12324,7 +12312,7 @@
     <row r="441">
       <c r="B441" t="inlineStr">
         <is>
-          <t>OCT250440</t>
+          <t>OCT250777</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -12351,7 +12339,7 @@
     <row r="442">
       <c r="B442" t="inlineStr">
         <is>
-          <t>OCT250441</t>
+          <t>OCT250778</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -12378,7 +12366,7 @@
     <row r="443">
       <c r="B443" t="inlineStr">
         <is>
-          <t>OCT250442</t>
+          <t>OCT250779</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -12405,7 +12393,7 @@
     <row r="444">
       <c r="B444" t="inlineStr">
         <is>
-          <t>OCT250443</t>
+          <t>OCT250780</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12432,7 +12420,7 @@
     <row r="445">
       <c r="B445" t="inlineStr">
         <is>
-          <t>OCT250444</t>
+          <t>OCT250781</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -12459,7 +12447,7 @@
     <row r="446">
       <c r="B446" t="inlineStr">
         <is>
-          <t>OCT250445</t>
+          <t>OCT250782</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -12486,7 +12474,7 @@
     <row r="447">
       <c r="B447" t="inlineStr">
         <is>
-          <t>OCT250446</t>
+          <t>OCT250783</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12513,7 +12501,7 @@
     <row r="448">
       <c r="B448" t="inlineStr">
         <is>
-          <t>OCT250447</t>
+          <t>OCT250784</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -12540,7 +12528,7 @@
     <row r="449">
       <c r="B449" t="inlineStr">
         <is>
-          <t>OCT250448</t>
+          <t>OCT250785</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -12567,7 +12555,7 @@
     <row r="450">
       <c r="B450" t="inlineStr">
         <is>
-          <t>OCT250449</t>
+          <t>OCT250786</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -12594,7 +12582,7 @@
     <row r="451">
       <c r="B451" t="inlineStr">
         <is>
-          <t>OCT250450</t>
+          <t>OCT250787</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12621,7 +12609,7 @@
     <row r="452">
       <c r="B452" t="inlineStr">
         <is>
-          <t>OCT250451</t>
+          <t>OCT250788</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -12648,7 +12636,7 @@
     <row r="453">
       <c r="B453" t="inlineStr">
         <is>
-          <t>OCT250452</t>
+          <t>OCT250789</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -12675,7 +12663,7 @@
     <row r="454">
       <c r="B454" t="inlineStr">
         <is>
-          <t>OCT250453</t>
+          <t>OCT250790</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -12702,7 +12690,7 @@
     <row r="455">
       <c r="B455" t="inlineStr">
         <is>
-          <t>OCT250454</t>
+          <t>OCT250791</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -12729,7 +12717,7 @@
     <row r="456">
       <c r="B456" t="inlineStr">
         <is>
-          <t>OCT250455</t>
+          <t>OCT250792</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -12756,7 +12744,7 @@
     <row r="457">
       <c r="B457" t="inlineStr">
         <is>
-          <t>OCT250456</t>
+          <t>OCT250793</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -12783,7 +12771,7 @@
     <row r="458">
       <c r="B458" t="inlineStr">
         <is>
-          <t>OCT250457</t>
+          <t>OCT250794</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -12810,7 +12798,7 @@
     <row r="459">
       <c r="B459" t="inlineStr">
         <is>
-          <t>OCT250458</t>
+          <t>OCT250795</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -12837,7 +12825,7 @@
     <row r="460">
       <c r="B460" t="inlineStr">
         <is>
-          <t>OCT250459</t>
+          <t>OCT250796</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12864,7 +12852,7 @@
     <row r="461">
       <c r="B461" t="inlineStr">
         <is>
-          <t>OCT250460</t>
+          <t>OCT250797</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12891,7 +12879,7 @@
     <row r="462">
       <c r="B462" t="inlineStr">
         <is>
-          <t>OCT250461</t>
+          <t>OCT250798</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12918,7 +12906,7 @@
     <row r="463">
       <c r="B463" t="inlineStr">
         <is>
-          <t>OCT250462</t>
+          <t>OCT250799</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12945,7 +12933,7 @@
     <row r="464">
       <c r="B464" t="inlineStr">
         <is>
-          <t>OCT250463</t>
+          <t>OCT250800</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12972,7 +12960,7 @@
     <row r="465">
       <c r="B465" t="inlineStr">
         <is>
-          <t>OCT250464</t>
+          <t>OCT250801</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12999,7 +12987,7 @@
     <row r="466">
       <c r="B466" t="inlineStr">
         <is>
-          <t>OCT250465</t>
+          <t>OCT250802</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -13026,7 +13014,7 @@
     <row r="467">
       <c r="B467" t="inlineStr">
         <is>
-          <t>OCT250466</t>
+          <t>OCT250803</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -13053,7 +13041,7 @@
     <row r="468">
       <c r="B468" t="inlineStr">
         <is>
-          <t>OCT250467</t>
+          <t>OCT250804</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13080,7 +13068,7 @@
     <row r="469">
       <c r="B469" t="inlineStr">
         <is>
-          <t>OCT250468</t>
+          <t>OCT250805</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13107,7 +13095,7 @@
     <row r="470">
       <c r="B470" t="inlineStr">
         <is>
-          <t>OCT250469</t>
+          <t>OCT250806</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -13134,7 +13122,7 @@
     <row r="471">
       <c r="B471" t="inlineStr">
         <is>
-          <t>OCT250470</t>
+          <t>OCT250807</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13161,7 +13149,7 @@
     <row r="472">
       <c r="B472" t="inlineStr">
         <is>
-          <t>OCT250471</t>
+          <t>OCT250808</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -13188,7 +13176,7 @@
     <row r="473">
       <c r="B473" t="inlineStr">
         <is>
-          <t>OCT250472</t>
+          <t>OCT250809</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13215,7 +13203,7 @@
     <row r="474">
       <c r="B474" t="inlineStr">
         <is>
-          <t>OCT250473</t>
+          <t>OCT250810</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -13242,7 +13230,7 @@
     <row r="475">
       <c r="B475" t="inlineStr">
         <is>
-          <t>OCT250474</t>
+          <t>OCT250811</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13269,7 +13257,7 @@
     <row r="476">
       <c r="B476" t="inlineStr">
         <is>
-          <t>OCT250475</t>
+          <t>OCT250812</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -13296,7 +13284,7 @@
     <row r="477">
       <c r="B477" t="inlineStr">
         <is>
-          <t>OCT250476</t>
+          <t>OCT250813</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -13323,7 +13311,7 @@
     <row r="478">
       <c r="B478" t="inlineStr">
         <is>
-          <t>OCT250477</t>
+          <t>OCT250814</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -13350,7 +13338,7 @@
     <row r="479">
       <c r="B479" t="inlineStr">
         <is>
-          <t>OCT250478</t>
+          <t>OCT250815</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -13377,7 +13365,7 @@
     <row r="480">
       <c r="B480" t="inlineStr">
         <is>
-          <t>OCT250479</t>
+          <t>OCT250816</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -13404,7 +13392,7 @@
     <row r="481">
       <c r="B481" t="inlineStr">
         <is>
-          <t>OCT250480</t>
+          <t>OCT250817</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -13431,7 +13419,7 @@
     <row r="482">
       <c r="B482" t="inlineStr">
         <is>
-          <t>OCT250481</t>
+          <t>OCT250818</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -13458,7 +13446,7 @@
     <row r="483">
       <c r="B483" t="inlineStr">
         <is>
-          <t>OCT250482</t>
+          <t>OCT250819</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13485,7 +13473,7 @@
     <row r="484">
       <c r="B484" t="inlineStr">
         <is>
-          <t>OCT250483</t>
+          <t>OCT250820</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -13512,7 +13500,7 @@
     <row r="485">
       <c r="B485" t="inlineStr">
         <is>
-          <t>OCT250484</t>
+          <t>OCT250821</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -13539,7 +13527,7 @@
     <row r="486">
       <c r="B486" t="inlineStr">
         <is>
-          <t>OCT250485</t>
+          <t>OCT250822</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -13566,7 +13554,7 @@
     <row r="487">
       <c r="B487" t="inlineStr">
         <is>
-          <t>OCT250486</t>
+          <t>OCT250823</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -13593,7 +13581,7 @@
     <row r="488">
       <c r="B488" t="inlineStr">
         <is>
-          <t>OCT250487</t>
+          <t>OCT250824</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -13620,7 +13608,7 @@
     <row r="489">
       <c r="B489" t="inlineStr">
         <is>
-          <t>OCT250488</t>
+          <t>OCT250825</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -13647,7 +13635,7 @@
     <row r="490">
       <c r="B490" t="inlineStr">
         <is>
-          <t>OCT250489</t>
+          <t>OCT250826</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -13674,7 +13662,7 @@
     <row r="491">
       <c r="B491" t="inlineStr">
         <is>
-          <t>OCT250490</t>
+          <t>OCT250827</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -13701,7 +13689,7 @@
     <row r="492">
       <c r="B492" t="inlineStr">
         <is>
-          <t>OCT250491</t>
+          <t>OCT250828</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13728,7 +13716,7 @@
     <row r="493">
       <c r="B493" t="inlineStr">
         <is>
-          <t>OCT250492</t>
+          <t>OCT250829</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13755,7 +13743,7 @@
     <row r="494">
       <c r="B494" t="inlineStr">
         <is>
-          <t>OCT250493</t>
+          <t>OCT250830</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13782,7 +13770,7 @@
     <row r="495">
       <c r="B495" t="inlineStr">
         <is>
-          <t>OCT250494</t>
+          <t>OCT250831</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13809,7 +13797,7 @@
     <row r="496">
       <c r="B496" t="inlineStr">
         <is>
-          <t>OCT250495</t>
+          <t>OCT250832</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13836,7 +13824,7 @@
     <row r="497">
       <c r="B497" t="inlineStr">
         <is>
-          <t>OCT250496</t>
+          <t>OCT250833</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13863,7 +13851,7 @@
     <row r="498">
       <c r="B498" t="inlineStr">
         <is>
-          <t>OCT250497</t>
+          <t>OCT250834</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13890,7 +13878,7 @@
     <row r="499">
       <c r="B499" t="inlineStr">
         <is>
-          <t>OCT250498</t>
+          <t>OCT250835</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13917,7 +13905,7 @@
     <row r="500">
       <c r="B500" t="inlineStr">
         <is>
-          <t>OCT250499</t>
+          <t>OCT250836</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13944,7 +13932,7 @@
     <row r="501">
       <c r="B501" t="inlineStr">
         <is>
-          <t>OCT250500</t>
+          <t>OCT250837</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -13971,7 +13959,7 @@
     <row r="502">
       <c r="B502" t="inlineStr">
         <is>
-          <t>OCT250501</t>
+          <t>OCT250838</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -13998,7 +13986,7 @@
     <row r="503">
       <c r="B503" t="inlineStr">
         <is>
-          <t>OCT250502</t>
+          <t>OCT250839</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -14025,7 +14013,7 @@
     <row r="504">
       <c r="B504" t="inlineStr">
         <is>
-          <t>OCT250503</t>
+          <t>OCT250840</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -14052,7 +14040,7 @@
     <row r="505">
       <c r="B505" t="inlineStr">
         <is>
-          <t>OCT250504</t>
+          <t>OCT250841</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -14079,7 +14067,7 @@
     <row r="506">
       <c r="B506" t="inlineStr">
         <is>
-          <t>OCT250505</t>
+          <t>OCT250842</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -14106,7 +14094,7 @@
     <row r="507">
       <c r="B507" t="inlineStr">
         <is>
-          <t>OCT250506</t>
+          <t>OCT250843</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -14133,7 +14121,7 @@
     <row r="508">
       <c r="B508" t="inlineStr">
         <is>
-          <t>OCT250507</t>
+          <t>OCT250844</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -14160,7 +14148,7 @@
     <row r="509">
       <c r="B509" t="inlineStr">
         <is>
-          <t>OCT250508</t>
+          <t>OCT250845</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14187,7 +14175,7 @@
     <row r="510">
       <c r="B510" t="inlineStr">
         <is>
-          <t>OCT250509</t>
+          <t>OCT250846</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14214,7 +14202,7 @@
     <row r="511">
       <c r="B511" t="inlineStr">
         <is>
-          <t>OCT250510</t>
+          <t>OCT250847</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14241,7 +14229,7 @@
     <row r="512">
       <c r="B512" t="inlineStr">
         <is>
-          <t>OCT250511</t>
+          <t>OCT250848</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14268,7 +14256,7 @@
     <row r="513">
       <c r="B513" t="inlineStr">
         <is>
-          <t>OCT250512</t>
+          <t>OCT250849</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14295,7 +14283,7 @@
     <row r="514">
       <c r="B514" t="inlineStr">
         <is>
-          <t>OCT250513</t>
+          <t>OCT250850</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -14322,7 +14310,7 @@
     <row r="515">
       <c r="B515" t="inlineStr">
         <is>
-          <t>OCT250514</t>
+          <t>OCT250851</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -14349,7 +14337,7 @@
     <row r="516">
       <c r="B516" t="inlineStr">
         <is>
-          <t>OCT250515</t>
+          <t>OCT250852</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -14376,7 +14364,7 @@
     <row r="517">
       <c r="B517" t="inlineStr">
         <is>
-          <t>OCT250516</t>
+          <t>OCT250853</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -14403,7 +14391,7 @@
     <row r="518">
       <c r="B518" t="inlineStr">
         <is>
-          <t>OCT250517</t>
+          <t>OCT250854</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -14430,7 +14418,7 @@
     <row r="519">
       <c r="B519" t="inlineStr">
         <is>
-          <t>OCT250518</t>
+          <t>OCT250855</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -14457,7 +14445,7 @@
     <row r="520">
       <c r="B520" t="inlineStr">
         <is>
-          <t>OCT250519</t>
+          <t>OCT250856</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -14484,7 +14472,7 @@
     <row r="521">
       <c r="B521" t="inlineStr">
         <is>
-          <t>OCT250520</t>
+          <t>OCT250857</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -14511,7 +14499,7 @@
     <row r="522">
       <c r="B522" t="inlineStr">
         <is>
-          <t>OCT250521</t>
+          <t>OCT250858</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -14538,7 +14526,7 @@
     <row r="523">
       <c r="B523" t="inlineStr">
         <is>
-          <t>OCT250522</t>
+          <t>OCT250859</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -14565,7 +14553,7 @@
     <row r="524">
       <c r="B524" t="inlineStr">
         <is>
-          <t>OCT250523</t>
+          <t>OCT250860</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -14592,7 +14580,7 @@
     <row r="525">
       <c r="B525" t="inlineStr">
         <is>
-          <t>OCT250524</t>
+          <t>OCT250861</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -14619,7 +14607,7 @@
     <row r="526">
       <c r="B526" t="inlineStr">
         <is>
-          <t>OCT250525</t>
+          <t>OCT250862</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -14646,7 +14634,7 @@
     <row r="527">
       <c r="B527" t="inlineStr">
         <is>
-          <t>OCT250526</t>
+          <t>OCT250863</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -14673,7 +14661,7 @@
     <row r="528">
       <c r="B528" t="inlineStr">
         <is>
-          <t>OCT250527</t>
+          <t>OCT250864</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -14700,7 +14688,7 @@
     <row r="529">
       <c r="B529" t="inlineStr">
         <is>
-          <t>OCT250528</t>
+          <t>OCT250865</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -14727,7 +14715,7 @@
     <row r="530">
       <c r="B530" t="inlineStr">
         <is>
-          <t>OCT250529</t>
+          <t>OCT250866</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -14754,7 +14742,7 @@
     <row r="531">
       <c r="B531" t="inlineStr">
         <is>
-          <t>OCT250530</t>
+          <t>OCT250867</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -14781,7 +14769,7 @@
     <row r="532">
       <c r="B532" t="inlineStr">
         <is>
-          <t>OCT250531</t>
+          <t>OCT250868</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -14808,7 +14796,7 @@
     <row r="533">
       <c r="B533" t="inlineStr">
         <is>
-          <t>OCT250532</t>
+          <t>OCT250869</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -14835,7 +14823,7 @@
     <row r="534">
       <c r="B534" t="inlineStr">
         <is>
-          <t>OCT250533</t>
+          <t>OCT250870</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -14862,7 +14850,7 @@
     <row r="535">
       <c r="B535" t="inlineStr">
         <is>
-          <t>OCT250534</t>
+          <t>OCT250871</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -14889,7 +14877,7 @@
     <row r="536">
       <c r="B536" t="inlineStr">
         <is>
-          <t>OCT250535</t>
+          <t>OCT250872</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -14916,7 +14904,7 @@
     <row r="537">
       <c r="B537" t="inlineStr">
         <is>
-          <t>OCT250536</t>
+          <t>OCT250873</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -14943,7 +14931,7 @@
     <row r="538">
       <c r="B538" t="inlineStr">
         <is>
-          <t>OCT250537</t>
+          <t>OCT250874</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14970,7 +14958,7 @@
     <row r="539">
       <c r="B539" t="inlineStr">
         <is>
-          <t>OCT250538</t>
+          <t>OCT250875</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -14997,7 +14985,7 @@
     <row r="540">
       <c r="B540" t="inlineStr">
         <is>
-          <t>OCT250539</t>
+          <t>OCT250876</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -15024,7 +15012,7 @@
     <row r="541">
       <c r="B541" t="inlineStr">
         <is>
-          <t>OCT250540</t>
+          <t>OCT250877</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -15051,7 +15039,7 @@
     <row r="542">
       <c r="B542" t="inlineStr">
         <is>
-          <t>OCT250541</t>
+          <t>OCT250878</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -15078,7 +15066,7 @@
     <row r="543">
       <c r="B543" t="inlineStr">
         <is>
-          <t>OCT250542</t>
+          <t>OCT250879</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -15105,7 +15093,7 @@
     <row r="544">
       <c r="B544" t="inlineStr">
         <is>
-          <t>OCT250543</t>
+          <t>OCT250880</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15132,7 +15120,7 @@
     <row r="545">
       <c r="B545" t="inlineStr">
         <is>
-          <t>OCT250544</t>
+          <t>OCT250881</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -15159,7 +15147,7 @@
     <row r="546">
       <c r="B546" t="inlineStr">
         <is>
-          <t>OCT250545</t>
+          <t>OCT250882</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -15186,7 +15174,7 @@
     <row r="547">
       <c r="B547" t="inlineStr">
         <is>
-          <t>OCT250546</t>
+          <t>OCT250883</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -15213,7 +15201,7 @@
     <row r="548">
       <c r="B548" t="inlineStr">
         <is>
-          <t>OCT250547</t>
+          <t>OCT250884</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -15240,7 +15228,7 @@
     <row r="549">
       <c r="B549" t="inlineStr">
         <is>
-          <t>OCT250548</t>
+          <t>OCT250885</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -15267,7 +15255,7 @@
     <row r="550">
       <c r="B550" t="inlineStr">
         <is>
-          <t>OCT250549</t>
+          <t>OCT250886</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -15294,7 +15282,7 @@
     <row r="551">
       <c r="B551" t="inlineStr">
         <is>
-          <t>OCT250550</t>
+          <t>OCT250887</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15321,7 +15309,7 @@
     <row r="552">
       <c r="B552" t="inlineStr">
         <is>
-          <t>OCT250551</t>
+          <t>OCT250888</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -15348,7 +15336,7 @@
     <row r="553">
       <c r="B553" t="inlineStr">
         <is>
-          <t>OCT250552</t>
+          <t>OCT250889</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15375,7 +15363,7 @@
     <row r="554">
       <c r="B554" t="inlineStr">
         <is>
-          <t>OCT250553</t>
+          <t>OCT250890</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -15402,7 +15390,7 @@
     <row r="555">
       <c r="B555" t="inlineStr">
         <is>
-          <t>OCT250554</t>
+          <t>OCT250891</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -15429,7 +15417,7 @@
     <row r="556">
       <c r="B556" t="inlineStr">
         <is>
-          <t>OCT250555</t>
+          <t>OCT250892</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -15456,7 +15444,7 @@
     <row r="557">
       <c r="B557" t="inlineStr">
         <is>
-          <t>OCT250556</t>
+          <t>OCT250893</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -15483,7 +15471,7 @@
     <row r="558">
       <c r="B558" t="inlineStr">
         <is>
-          <t>OCT250557</t>
+          <t>OCT250894</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -15510,7 +15498,7 @@
     <row r="559">
       <c r="B559" t="inlineStr">
         <is>
-          <t>OCT250558</t>
+          <t>OCT250895</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -15537,7 +15525,7 @@
     <row r="560">
       <c r="B560" t="inlineStr">
         <is>
-          <t>OCT250559</t>
+          <t>OCT250896</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -15564,7 +15552,7 @@
     <row r="561">
       <c r="B561" t="inlineStr">
         <is>
-          <t>OCT250560</t>
+          <t>OCT250897</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -15591,7 +15579,7 @@
     <row r="562">
       <c r="B562" t="inlineStr">
         <is>
-          <t>OCT250561</t>
+          <t>OCT250898</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -15618,7 +15606,7 @@
     <row r="563">
       <c r="B563" t="inlineStr">
         <is>
-          <t>OCT250562</t>
+          <t>OCT250899</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -15645,7 +15633,7 @@
     <row r="564">
       <c r="B564" t="inlineStr">
         <is>
-          <t>OCT250563</t>
+          <t>OCT250900</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -15672,7 +15660,7 @@
     <row r="565">
       <c r="B565" t="inlineStr">
         <is>
-          <t>OCT250564</t>
+          <t>OCT250901</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -15699,7 +15687,7 @@
     <row r="566">
       <c r="B566" t="inlineStr">
         <is>
-          <t>OCT250565</t>
+          <t>OCT250902</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -15726,7 +15714,7 @@
     <row r="567">
       <c r="B567" t="inlineStr">
         <is>
-          <t>OCT250566</t>
+          <t>OCT250903</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -15753,7 +15741,7 @@
     <row r="568">
       <c r="B568" t="inlineStr">
         <is>
-          <t>OCT250567</t>
+          <t>OCT250904</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -15780,7 +15768,7 @@
     <row r="569">
       <c r="B569" t="inlineStr">
         <is>
-          <t>OCT250568</t>
+          <t>OCT250905</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -15807,7 +15795,7 @@
     <row r="570">
       <c r="B570" t="inlineStr">
         <is>
-          <t>OCT250569</t>
+          <t>OCT250906</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -15834,7 +15822,7 @@
     <row r="571">
       <c r="B571" t="inlineStr">
         <is>
-          <t>OCT250570</t>
+          <t>OCT250907</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -15861,7 +15849,7 @@
     <row r="572">
       <c r="B572" t="inlineStr">
         <is>
-          <t>OCT250571</t>
+          <t>OCT250908</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -15888,7 +15876,7 @@
     <row r="573">
       <c r="B573" t="inlineStr">
         <is>
-          <t>OCT250572</t>
+          <t>OCT250909</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15915,7 +15903,7 @@
     <row r="574">
       <c r="B574" t="inlineStr">
         <is>
-          <t>OCT250573</t>
+          <t>OCT250910</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -15942,7 +15930,7 @@
     <row r="575">
       <c r="B575" t="inlineStr">
         <is>
-          <t>OCT250574</t>
+          <t>OCT250911</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -15969,7 +15957,7 @@
     <row r="576">
       <c r="B576" t="inlineStr">
         <is>
-          <t>OCT250575</t>
+          <t>OCT250912</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -15996,7 +15984,7 @@
     <row r="577">
       <c r="B577" t="inlineStr">
         <is>
-          <t>OCT250576</t>
+          <t>OCT250913</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -16023,7 +16011,7 @@
     <row r="578">
       <c r="B578" t="inlineStr">
         <is>
-          <t>OCT250577</t>
+          <t>OCT250914</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -16050,7 +16038,7 @@
     <row r="579">
       <c r="B579" t="inlineStr">
         <is>
-          <t>OCT250578</t>
+          <t>OCT250915</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -16077,7 +16065,7 @@
     <row r="580">
       <c r="B580" t="inlineStr">
         <is>
-          <t>OCT250579</t>
+          <t>OCT250916</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -16104,7 +16092,7 @@
     <row r="581">
       <c r="B581" t="inlineStr">
         <is>
-          <t>OCT250580</t>
+          <t>OCT250917</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -16131,7 +16119,7 @@
     <row r="582">
       <c r="B582" t="inlineStr">
         <is>
-          <t>OCT250581</t>
+          <t>OCT250918</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16158,7 +16146,7 @@
     <row r="583">
       <c r="B583" t="inlineStr">
         <is>
-          <t>OCT250582</t>
+          <t>OCT250919</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16185,7 +16173,7 @@
     <row r="584">
       <c r="B584" t="inlineStr">
         <is>
-          <t>OCT250583</t>
+          <t>OCT250920</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -16212,7 +16200,7 @@
     <row r="585">
       <c r="B585" t="inlineStr">
         <is>
-          <t>OCT250584</t>
+          <t>OCT250921</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -16239,7 +16227,7 @@
     <row r="586">
       <c r="B586" t="inlineStr">
         <is>
-          <t>OCT250585</t>
+          <t>OCT250922</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -16266,7 +16254,7 @@
     <row r="587">
       <c r="B587" t="inlineStr">
         <is>
-          <t>OCT250586</t>
+          <t>OCT250923</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -16293,7 +16281,7 @@
     <row r="588">
       <c r="B588" t="inlineStr">
         <is>
-          <t>OCT250587</t>
+          <t>OCT250924</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -16320,7 +16308,7 @@
     <row r="589">
       <c r="B589" t="inlineStr">
         <is>
-          <t>OCT250588</t>
+          <t>OCT250925</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -16347,7 +16335,7 @@
     <row r="590">
       <c r="B590" t="inlineStr">
         <is>
-          <t>OCT250589</t>
+          <t>OCT250926</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -16374,7 +16362,7 @@
     <row r="591">
       <c r="B591" t="inlineStr">
         <is>
-          <t>OCT250590</t>
+          <t>OCT250927</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -16401,7 +16389,7 @@
     <row r="592">
       <c r="B592" t="inlineStr">
         <is>
-          <t>OCT250591</t>
+          <t>OCT250928</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -16428,7 +16416,7 @@
     <row r="593">
       <c r="B593" t="inlineStr">
         <is>
-          <t>OCT250592</t>
+          <t>OCT250929</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -16455,7 +16443,7 @@
     <row r="594">
       <c r="B594" t="inlineStr">
         <is>
-          <t>OCT250593</t>
+          <t>OCT250930</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -16482,7 +16470,7 @@
     <row r="595">
       <c r="B595" t="inlineStr">
         <is>
-          <t>OCT250594</t>
+          <t>OCT250931</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -16509,7 +16497,7 @@
     <row r="596">
       <c r="B596" t="inlineStr">
         <is>
-          <t>OCT250595</t>
+          <t>OCT250932</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -16536,7 +16524,7 @@
     <row r="597">
       <c r="B597" t="inlineStr">
         <is>
-          <t>OCT250596</t>
+          <t>OCT250933</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -16563,7 +16551,7 @@
     <row r="598">
       <c r="B598" t="inlineStr">
         <is>
-          <t>OCT250597</t>
+          <t>OCT250934</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -16590,7 +16578,7 @@
     <row r="599">
       <c r="B599" t="inlineStr">
         <is>
-          <t>OCT250598</t>
+          <t>OCT250935</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -16617,7 +16605,7 @@
     <row r="600">
       <c r="B600" t="inlineStr">
         <is>
-          <t>OCT250599</t>
+          <t>OCT250936</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -16644,7 +16632,7 @@
     <row r="601">
       <c r="B601" t="inlineStr">
         <is>
-          <t>OCT250600</t>
+          <t>OCT250937</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -16671,7 +16659,7 @@
     <row r="602">
       <c r="B602" t="inlineStr">
         <is>
-          <t>OCT250601</t>
+          <t>OCT250938</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -16698,7 +16686,7 @@
     <row r="603">
       <c r="B603" t="inlineStr">
         <is>
-          <t>OCT250602</t>
+          <t>OCT250939</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -16725,7 +16713,7 @@
     <row r="604">
       <c r="B604" t="inlineStr">
         <is>
-          <t>OCT250603</t>
+          <t>OCT250940</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -16752,7 +16740,7 @@
     <row r="605">
       <c r="B605" t="inlineStr">
         <is>
-          <t>OCT250604</t>
+          <t>OCT250941</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -16779,7 +16767,7 @@
     <row r="606">
       <c r="B606" t="inlineStr">
         <is>
-          <t>OCT250605</t>
+          <t>OCT250942</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -16806,7 +16794,7 @@
     <row r="607">
       <c r="B607" t="inlineStr">
         <is>
-          <t>OCT250606</t>
+          <t>OCT250943</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -16833,7 +16821,7 @@
     <row r="608">
       <c r="B608" t="inlineStr">
         <is>
-          <t>OCT250607</t>
+          <t>OCT250944</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -16860,7 +16848,7 @@
     <row r="609">
       <c r="B609" t="inlineStr">
         <is>
-          <t>OCT250608</t>
+          <t>OCT250945</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -16887,7 +16875,7 @@
     <row r="610">
       <c r="B610" t="inlineStr">
         <is>
-          <t>OCT250609</t>
+          <t>OCT250946</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -16914,7 +16902,7 @@
     <row r="611">
       <c r="B611" t="inlineStr">
         <is>
-          <t>OCT250610</t>
+          <t>OCT250947</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -16941,7 +16929,7 @@
     <row r="612">
       <c r="B612" t="inlineStr">
         <is>
-          <t>OCT250611</t>
+          <t>OCT250948</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -16968,7 +16956,7 @@
     <row r="613">
       <c r="B613" t="inlineStr">
         <is>
-          <t>OCT250612</t>
+          <t>OCT250949</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16995,7 +16983,7 @@
     <row r="614">
       <c r="B614" t="inlineStr">
         <is>
-          <t>OCT250613</t>
+          <t>OCT250950</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -17022,7 +17010,7 @@
     <row r="615">
       <c r="B615" t="inlineStr">
         <is>
-          <t>OCT250614</t>
+          <t>OCT250951</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -17049,7 +17037,7 @@
     <row r="616">
       <c r="B616" t="inlineStr">
         <is>
-          <t>OCT250615</t>
+          <t>OCT250952</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -17076,7 +17064,7 @@
     <row r="617">
       <c r="B617" t="inlineStr">
         <is>
-          <t>OCT250616</t>
+          <t>OCT250953</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -17103,7 +17091,7 @@
     <row r="618">
       <c r="B618" t="inlineStr">
         <is>
-          <t>OCT250617</t>
+          <t>OCT250954</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17130,7 +17118,7 @@
     <row r="619">
       <c r="B619" t="inlineStr">
         <is>
-          <t>OCT250618</t>
+          <t>OCT250955</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -17157,7 +17145,7 @@
     <row r="620">
       <c r="B620" t="inlineStr">
         <is>
-          <t>OCT250619</t>
+          <t>OCT250956</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -17184,7 +17172,7 @@
     <row r="621">
       <c r="B621" t="inlineStr">
         <is>
-          <t>OCT250620</t>
+          <t>OCT250957</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -17211,7 +17199,7 @@
     <row r="622">
       <c r="B622" t="inlineStr">
         <is>
-          <t>OCT250621</t>
+          <t>OCT250958</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -17238,7 +17226,7 @@
     <row r="623">
       <c r="B623" t="inlineStr">
         <is>
-          <t>OCT250622</t>
+          <t>OCT250959</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17265,7 +17253,7 @@
     <row r="624">
       <c r="B624" t="inlineStr">
         <is>
-          <t>OCT250623</t>
+          <t>OCT250960</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -17292,7 +17280,7 @@
     <row r="625">
       <c r="B625" t="inlineStr">
         <is>
-          <t>OCT250624</t>
+          <t>OCT250961</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -17319,7 +17307,7 @@
     <row r="626">
       <c r="B626" t="inlineStr">
         <is>
-          <t>OCT250625</t>
+          <t>OCT250962</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -17346,7 +17334,7 @@
     <row r="627">
       <c r="B627" t="inlineStr">
         <is>
-          <t>OCT250626</t>
+          <t>OCT250963</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -17373,7 +17361,7 @@
     <row r="628">
       <c r="B628" t="inlineStr">
         <is>
-          <t>OCT250627</t>
+          <t>OCT250964</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -17400,7 +17388,7 @@
     <row r="629">
       <c r="B629" t="inlineStr">
         <is>
-          <t>OCT250628</t>
+          <t>OCT250965</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -17427,7 +17415,7 @@
     <row r="630">
       <c r="B630" t="inlineStr">
         <is>
-          <t>OCT250629</t>
+          <t>OCT250966</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -17454,7 +17442,7 @@
     <row r="631">
       <c r="B631" t="inlineStr">
         <is>
-          <t>OCT250630</t>
+          <t>OCT250967</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -17481,7 +17469,7 @@
     <row r="632">
       <c r="B632" t="inlineStr">
         <is>
-          <t>OCT250631</t>
+          <t>OCT250968</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -17508,7 +17496,7 @@
     <row r="633">
       <c r="B633" t="inlineStr">
         <is>
-          <t>OCT250632</t>
+          <t>OCT250969</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -17535,7 +17523,7 @@
     <row r="634">
       <c r="B634" t="inlineStr">
         <is>
-          <t>OCT250633</t>
+          <t>OCT250970</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -17562,7 +17550,7 @@
     <row r="635">
       <c r="B635" t="inlineStr">
         <is>
-          <t>OCT250634</t>
+          <t>OCT250971</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -17589,7 +17577,7 @@
     <row r="636">
       <c r="B636" t="inlineStr">
         <is>
-          <t>OCT250635</t>
+          <t>OCT250972</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -17616,7 +17604,7 @@
     <row r="637">
       <c r="B637" t="inlineStr">
         <is>
-          <t>OCT250636</t>
+          <t>OCT250973</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -17643,7 +17631,7 @@
     <row r="638">
       <c r="B638" t="inlineStr">
         <is>
-          <t>OCT250637</t>
+          <t>OCT250974</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -17670,7 +17658,7 @@
     <row r="639">
       <c r="B639" t="inlineStr">
         <is>
-          <t>OCT250638</t>
+          <t>OCT250975</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -17697,7 +17685,7 @@
     <row r="640">
       <c r="B640" t="inlineStr">
         <is>
-          <t>OCT250639</t>
+          <t>OCT250976</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -17724,7 +17712,7 @@
     <row r="641">
       <c r="B641" t="inlineStr">
         <is>
-          <t>OCT250640</t>
+          <t>OCT250977</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -17751,7 +17739,7 @@
     <row r="642">
       <c r="B642" t="inlineStr">
         <is>
-          <t>OCT250641</t>
+          <t>OCT250978</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -17778,7 +17766,7 @@
     <row r="643">
       <c r="B643" t="inlineStr">
         <is>
-          <t>OCT250642</t>
+          <t>OCT250979</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -17805,7 +17793,7 @@
     <row r="644">
       <c r="B644" t="inlineStr">
         <is>
-          <t>OCT250643</t>
+          <t>OCT250980</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -17832,7 +17820,7 @@
     <row r="645">
       <c r="B645" t="inlineStr">
         <is>
-          <t>OCT250644</t>
+          <t>OCT250981</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -17859,7 +17847,7 @@
     <row r="646">
       <c r="B646" t="inlineStr">
         <is>
-          <t>OCT250645</t>
+          <t>OCT250982</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -17886,7 +17874,7 @@
     <row r="647">
       <c r="B647" t="inlineStr">
         <is>
-          <t>OCT250646</t>
+          <t>OCT250983</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -17913,7 +17901,7 @@
     <row r="648">
       <c r="B648" t="inlineStr">
         <is>
-          <t>OCT250647</t>
+          <t>OCT250984</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -17940,7 +17928,7 @@
     <row r="649">
       <c r="B649" t="inlineStr">
         <is>
-          <t>OCT250648</t>
+          <t>OCT250985</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -17967,7 +17955,7 @@
     <row r="650">
       <c r="B650" t="inlineStr">
         <is>
-          <t>OCT250649</t>
+          <t>OCT250986</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -17994,7 +17982,7 @@
     <row r="651">
       <c r="B651" t="inlineStr">
         <is>
-          <t>OCT250650</t>
+          <t>OCT250987</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -18021,7 +18009,7 @@
     <row r="652">
       <c r="B652" t="inlineStr">
         <is>
-          <t>OCT250651</t>
+          <t>OCT250988</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -18048,7 +18036,7 @@
     <row r="653">
       <c r="B653" t="inlineStr">
         <is>
-          <t>OCT250652</t>
+          <t>OCT250989</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -18075,7 +18063,7 @@
     <row r="654">
       <c r="B654" t="inlineStr">
         <is>
-          <t>OCT250653</t>
+          <t>OCT250990</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -18102,7 +18090,7 @@
     <row r="655">
       <c r="B655" t="inlineStr">
         <is>
-          <t>OCT250654</t>
+          <t>OCT250991</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -18129,7 +18117,7 @@
     <row r="656">
       <c r="B656" t="inlineStr">
         <is>
-          <t>OCT250655</t>
+          <t>OCT250992</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -18156,7 +18144,7 @@
     <row r="657">
       <c r="B657" t="inlineStr">
         <is>
-          <t>OCT250656</t>
+          <t>OCT250993</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18183,7 +18171,7 @@
     <row r="658">
       <c r="B658" t="inlineStr">
         <is>
-          <t>OCT250657</t>
+          <t>OCT250994</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -18210,7 +18198,7 @@
     <row r="659">
       <c r="B659" t="inlineStr">
         <is>
-          <t>OCT250658</t>
+          <t>OCT250995</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18237,7 +18225,7 @@
     <row r="660">
       <c r="B660" t="inlineStr">
         <is>
-          <t>OCT250659</t>
+          <t>OCT250996</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -18264,7 +18252,7 @@
     <row r="661">
       <c r="B661" t="inlineStr">
         <is>
-          <t>OCT250660</t>
+          <t>OCT250997</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18291,7 +18279,7 @@
     <row r="662">
       <c r="B662" t="inlineStr">
         <is>
-          <t>OCT250661</t>
+          <t>OCT250998</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18318,7 +18306,7 @@
     <row r="663">
       <c r="B663" t="inlineStr">
         <is>
-          <t>OCT250662</t>
+          <t>OCT250999</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18345,7 +18333,7 @@
     <row r="664">
       <c r="B664" t="inlineStr">
         <is>
-          <t>OCT250663</t>
+          <t>OCT251000</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -18372,7 +18360,7 @@
     <row r="665">
       <c r="B665" t="inlineStr">
         <is>
-          <t>OCT250664</t>
+          <t>OCT251001</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18399,7 +18387,7 @@
     <row r="666">
       <c r="B666" t="inlineStr">
         <is>
-          <t>OCT250665</t>
+          <t>OCT251002</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18426,7 +18414,7 @@
     <row r="667">
       <c r="B667" t="inlineStr">
         <is>
-          <t>OCT250666</t>
+          <t>OCT251003</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18453,7 +18441,7 @@
     <row r="668">
       <c r="B668" t="inlineStr">
         <is>
-          <t>OCT250667</t>
+          <t>OCT251004</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -18480,7 +18468,7 @@
     <row r="669">
       <c r="B669" t="inlineStr">
         <is>
-          <t>OCT250668</t>
+          <t>OCT251005</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18507,7 +18495,7 @@
     <row r="670">
       <c r="B670" t="inlineStr">
         <is>
-          <t>OCT250669</t>
+          <t>OCT251006</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -18534,7 +18522,7 @@
     <row r="671">
       <c r="B671" t="inlineStr">
         <is>
-          <t>OCT250670</t>
+          <t>OCT251007</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18561,7 +18549,7 @@
     <row r="672">
       <c r="B672" t="inlineStr">
         <is>
-          <t>OCT250671</t>
+          <t>OCT251008</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -18588,7 +18576,7 @@
     <row r="673">
       <c r="B673" t="inlineStr">
         <is>
-          <t>OCT250672</t>
+          <t>OCT251009</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -18615,7 +18603,7 @@
     <row r="674">
       <c r="B674" t="inlineStr">
         <is>
-          <t>OCT250673</t>
+          <t>OCT251010</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -18642,7 +18630,7 @@
     <row r="675">
       <c r="B675" t="inlineStr">
         <is>
-          <t>OCT250674</t>
+          <t>OCT251011</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -18669,7 +18657,7 @@
     <row r="676">
       <c r="B676" t="inlineStr">
         <is>
-          <t>OCT250675</t>
+          <t>OCT251012</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -18696,7 +18684,7 @@
     <row r="677">
       <c r="B677" t="inlineStr">
         <is>
-          <t>OCT250676</t>
+          <t>OCT251013</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -18723,7 +18711,7 @@
     <row r="678">
       <c r="B678" t="inlineStr">
         <is>
-          <t>OCT250677</t>
+          <t>OCT251014</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -18750,7 +18738,7 @@
     <row r="679">
       <c r="B679" t="inlineStr">
         <is>
-          <t>OCT250678</t>
+          <t>OCT251015</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -18777,7 +18765,7 @@
     <row r="680">
       <c r="B680" t="inlineStr">
         <is>
-          <t>OCT250679</t>
+          <t>OCT251016</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -18804,7 +18792,7 @@
     <row r="681">
       <c r="B681" t="inlineStr">
         <is>
-          <t>OCT250680</t>
+          <t>OCT251017</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -18831,7 +18819,7 @@
     <row r="682">
       <c r="B682" t="inlineStr">
         <is>
-          <t>OCT250681</t>
+          <t>OCT251018</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -18858,7 +18846,7 @@
     <row r="683">
       <c r="B683" t="inlineStr">
         <is>
-          <t>OCT250682</t>
+          <t>OCT251019</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -18885,7 +18873,7 @@
     <row r="684">
       <c r="B684" t="inlineStr">
         <is>
-          <t>OCT250683</t>
+          <t>OCT251020</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -18912,7 +18900,7 @@
     <row r="685">
       <c r="B685" t="inlineStr">
         <is>
-          <t>OCT250684</t>
+          <t>OCT251021</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -18939,7 +18927,7 @@
     <row r="686">
       <c r="B686" t="inlineStr">
         <is>
-          <t>OCT250685</t>
+          <t>OCT251022</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -18966,7 +18954,7 @@
     <row r="687">
       <c r="B687" t="inlineStr">
         <is>
-          <t>OCT250686</t>
+          <t>OCT251023</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -18993,7 +18981,7 @@
     <row r="688">
       <c r="B688" t="inlineStr">
         <is>
-          <t>OCT250687</t>
+          <t>OCT251024</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -19020,7 +19008,7 @@
     <row r="689">
       <c r="B689" t="inlineStr">
         <is>
-          <t>OCT250688</t>
+          <t>OCT251025</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -19047,7 +19035,7 @@
     <row r="690">
       <c r="B690" t="inlineStr">
         <is>
-          <t>OCT250689</t>
+          <t>OCT251026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -19074,7 +19062,7 @@
     <row r="691">
       <c r="B691" t="inlineStr">
         <is>
-          <t>OCT250690</t>
+          <t>OCT251027</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19101,7 +19089,7 @@
     <row r="692">
       <c r="B692" t="inlineStr">
         <is>
-          <t>OCT250691</t>
+          <t>OCT251028</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19128,7 +19116,7 @@
     <row r="693">
       <c r="B693" t="inlineStr">
         <is>
-          <t>OCT250692</t>
+          <t>OCT251029</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -19155,7 +19143,7 @@
     <row r="694">
       <c r="B694" t="inlineStr">
         <is>
-          <t>OCT250693</t>
+          <t>OCT251030</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -19182,7 +19170,7 @@
     <row r="695">
       <c r="B695" t="inlineStr">
         <is>
-          <t>OCT250694</t>
+          <t>OCT251031</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19209,7 +19197,7 @@
     <row r="696">
       <c r="B696" t="inlineStr">
         <is>
-          <t>OCT250695</t>
+          <t>OCT251032</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -19236,7 +19224,7 @@
     <row r="697">
       <c r="B697" t="inlineStr">
         <is>
-          <t>OCT250696</t>
+          <t>OCT251033</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -19263,7 +19251,7 @@
     <row r="698">
       <c r="B698" t="inlineStr">
         <is>
-          <t>OCT250697</t>
+          <t>OCT251034</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19290,7 +19278,7 @@
     <row r="699">
       <c r="B699" t="inlineStr">
         <is>
-          <t>OCT250698</t>
+          <t>OCT251035</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19317,7 +19305,7 @@
     <row r="700">
       <c r="B700" t="inlineStr">
         <is>
-          <t>OCT250699</t>
+          <t>OCT251036</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -19344,7 +19332,7 @@
     <row r="701">
       <c r="B701" t="inlineStr">
         <is>
-          <t>OCT250700</t>
+          <t>OCT251037</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -19371,7 +19359,7 @@
     <row r="702">
       <c r="B702" t="inlineStr">
         <is>
-          <t>OCT250701</t>
+          <t>OCT251038</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -19398,7 +19386,7 @@
     <row r="703">
       <c r="B703" t="inlineStr">
         <is>
-          <t>OCT250702</t>
+          <t>OCT251039</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -19425,7 +19413,7 @@
     <row r="704">
       <c r="B704" t="inlineStr">
         <is>
-          <t>OCT250703</t>
+          <t>OCT251040</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -19452,7 +19440,7 @@
     <row r="705">
       <c r="B705" t="inlineStr">
         <is>
-          <t>OCT250704</t>
+          <t>OCT251041</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -19479,7 +19467,7 @@
     <row r="706">
       <c r="B706" t="inlineStr">
         <is>
-          <t>OCT250705</t>
+          <t>OCT251042</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -19506,7 +19494,7 @@
     <row r="707">
       <c r="B707" t="inlineStr">
         <is>
-          <t>OCT250706</t>
+          <t>OCT251043</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -19533,7 +19521,7 @@
     <row r="708">
       <c r="B708" t="inlineStr">
         <is>
-          <t>OCT250707</t>
+          <t>OCT251044</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -19560,7 +19548,7 @@
     <row r="709">
       <c r="B709" t="inlineStr">
         <is>
-          <t>OCT250708</t>
+          <t>OCT251045</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -19587,7 +19575,7 @@
     <row r="710">
       <c r="B710" t="inlineStr">
         <is>
-          <t>OCT250709</t>
+          <t>OCT251046</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -19614,7 +19602,7 @@
     <row r="711">
       <c r="B711" t="inlineStr">
         <is>
-          <t>OCT250710</t>
+          <t>OCT251047</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -19641,7 +19629,7 @@
     <row r="712">
       <c r="B712" t="inlineStr">
         <is>
-          <t>OCT250711</t>
+          <t>OCT251048</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -19668,7 +19656,7 @@
     <row r="713">
       <c r="B713" t="inlineStr">
         <is>
-          <t>OCT250712</t>
+          <t>OCT251049</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -19695,7 +19683,7 @@
     <row r="714">
       <c r="B714" t="inlineStr">
         <is>
-          <t>OCT250713</t>
+          <t>OCT251050</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -19722,7 +19710,7 @@
     <row r="715">
       <c r="B715" t="inlineStr">
         <is>
-          <t>OCT250714</t>
+          <t>OCT251051</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -19749,7 +19737,7 @@
     <row r="716">
       <c r="B716" t="inlineStr">
         <is>
-          <t>OCT250715</t>
+          <t>OCT251052</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -19776,7 +19764,7 @@
     <row r="717">
       <c r="B717" t="inlineStr">
         <is>
-          <t>OCT250716</t>
+          <t>OCT251053</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -19803,7 +19791,7 @@
     <row r="718">
       <c r="B718" t="inlineStr">
         <is>
-          <t>OCT250717</t>
+          <t>OCT251054</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -19830,7 +19818,7 @@
     <row r="719">
       <c r="B719" t="inlineStr">
         <is>
-          <t>OCT250718</t>
+          <t>OCT251055</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -19857,7 +19845,7 @@
     <row r="720">
       <c r="B720" t="inlineStr">
         <is>
-          <t>OCT250719</t>
+          <t>OCT251056</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -19884,7 +19872,7 @@
     <row r="721">
       <c r="B721" t="inlineStr">
         <is>
-          <t>OCT250720</t>
+          <t>OCT251057</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -19911,7 +19899,7 @@
     <row r="722">
       <c r="B722" t="inlineStr">
         <is>
-          <t>OCT250721</t>
+          <t>OCT251058</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -19938,7 +19926,7 @@
     <row r="723">
       <c r="B723" t="inlineStr">
         <is>
-          <t>OCT250722</t>
+          <t>OCT251059</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -19965,7 +19953,7 @@
     <row r="724">
       <c r="B724" t="inlineStr">
         <is>
-          <t>OCT250723</t>
+          <t>OCT251060</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -19992,7 +19980,7 @@
     <row r="725">
       <c r="B725" t="inlineStr">
         <is>
-          <t>OCT250724</t>
+          <t>OCT251061</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -20019,7 +20007,7 @@
     <row r="726">
       <c r="B726" t="inlineStr">
         <is>
-          <t>OCT250725</t>
+          <t>OCT251062</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -20046,7 +20034,7 @@
     <row r="727">
       <c r="B727" t="inlineStr">
         <is>
-          <t>OCT250726</t>
+          <t>OCT251063</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -20073,7 +20061,7 @@
     <row r="728">
       <c r="B728" t="inlineStr">
         <is>
-          <t>OCT250727</t>
+          <t>OCT251064</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -20100,7 +20088,7 @@
     <row r="729">
       <c r="B729" t="inlineStr">
         <is>
-          <t>OCT250728</t>
+          <t>OCT251065</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -20127,7 +20115,7 @@
     <row r="730">
       <c r="B730" t="inlineStr">
         <is>
-          <t>OCT250729</t>
+          <t>OCT251066</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -20154,7 +20142,7 @@
     <row r="731">
       <c r="B731" t="inlineStr">
         <is>
-          <t>OCT250730</t>
+          <t>OCT251067</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -20181,7 +20169,7 @@
     <row r="732">
       <c r="B732" t="inlineStr">
         <is>
-          <t>OCT250731</t>
+          <t>OCT251068</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -20208,7 +20196,7 @@
     <row r="733">
       <c r="B733" t="inlineStr">
         <is>
-          <t>OCT250732</t>
+          <t>OCT251069</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -20235,7 +20223,7 @@
     <row r="734">
       <c r="B734" t="inlineStr">
         <is>
-          <t>OCT250733</t>
+          <t>OCT251070</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -20262,7 +20250,7 @@
     <row r="735">
       <c r="B735" t="inlineStr">
         <is>
-          <t>OCT250734</t>
+          <t>OCT251071</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -20289,7 +20277,7 @@
     <row r="736">
       <c r="B736" t="inlineStr">
         <is>
-          <t>OCT250735</t>
+          <t>OCT251072</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -20316,7 +20304,7 @@
     <row r="737">
       <c r="B737" t="inlineStr">
         <is>
-          <t>OCT250736</t>
+          <t>OCT251073</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20343,7 +20331,7 @@
     <row r="738">
       <c r="B738" t="inlineStr">
         <is>
-          <t>OCT250737</t>
+          <t>OCT251074</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -20370,7 +20358,7 @@
     <row r="739">
       <c r="B739" t="inlineStr">
         <is>
-          <t>OCT250738</t>
+          <t>OCT251075</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -20397,7 +20385,7 @@
     <row r="740">
       <c r="B740" t="inlineStr">
         <is>
-          <t>OCT250739</t>
+          <t>OCT251076</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -20424,7 +20412,7 @@
     <row r="741">
       <c r="B741" t="inlineStr">
         <is>
-          <t>OCT250740</t>
+          <t>OCT251077</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -20451,7 +20439,7 @@
     <row r="742">
       <c r="B742" t="inlineStr">
         <is>
-          <t>OCT250741</t>
+          <t>OCT251078</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -20478,7 +20466,7 @@
     <row r="743">
       <c r="B743" t="inlineStr">
         <is>
-          <t>OCT250742</t>
+          <t>OCT251079</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20505,7 +20493,7 @@
     <row r="744">
       <c r="B744" t="inlineStr">
         <is>
-          <t>OCT250743</t>
+          <t>OCT251080</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -20532,7 +20520,7 @@
     <row r="745">
       <c r="B745" t="inlineStr">
         <is>
-          <t>OCT250744</t>
+          <t>OCT251081</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -20559,7 +20547,7 @@
     <row r="746">
       <c r="B746" t="inlineStr">
         <is>
-          <t>OCT250745</t>
+          <t>OCT251082</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -20586,7 +20574,7 @@
     <row r="747">
       <c r="B747" t="inlineStr">
         <is>
-          <t>OCT250746</t>
+          <t>OCT251083</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -20613,7 +20601,7 @@
     <row r="748">
       <c r="B748" t="inlineStr">
         <is>
-          <t>OCT250747</t>
+          <t>OCT251084</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -20640,7 +20628,7 @@
     <row r="749">
       <c r="B749" t="inlineStr">
         <is>
-          <t>OCT250748</t>
+          <t>OCT251085</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -20667,7 +20655,7 @@
     <row r="750">
       <c r="B750" t="inlineStr">
         <is>
-          <t>OCT250749</t>
+          <t>OCT251086</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -20694,7 +20682,7 @@
     <row r="751">
       <c r="B751" t="inlineStr">
         <is>
-          <t>OCT250750</t>
+          <t>OCT251087</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -20721,7 +20709,7 @@
     <row r="752">
       <c r="B752" t="inlineStr">
         <is>
-          <t>OCT250751</t>
+          <t>OCT251088</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -20748,7 +20736,7 @@
     <row r="753">
       <c r="B753" t="inlineStr">
         <is>
-          <t>OCT250752</t>
+          <t>OCT251089</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -20775,7 +20763,7 @@
     <row r="754">
       <c r="B754" t="inlineStr">
         <is>
-          <t>OCT250753</t>
+          <t>OCT251090</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -20802,7 +20790,7 @@
     <row r="755">
       <c r="B755" t="inlineStr">
         <is>
-          <t>OCT250754</t>
+          <t>OCT251091</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -20829,7 +20817,7 @@
     <row r="756">
       <c r="B756" t="inlineStr">
         <is>
-          <t>OCT250755</t>
+          <t>OCT251092</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -20856,7 +20844,7 @@
     <row r="757">
       <c r="B757" t="inlineStr">
         <is>
-          <t>OCT250756</t>
+          <t>OCT251093</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -20883,7 +20871,7 @@
     <row r="758">
       <c r="B758" t="inlineStr">
         <is>
-          <t>OCT250757</t>
+          <t>OCT251094</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -20910,7 +20898,7 @@
     <row r="759">
       <c r="B759" t="inlineStr">
         <is>
-          <t>OCT250758</t>
+          <t>OCT251095</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -20937,7 +20925,7 @@
     <row r="760">
       <c r="B760" t="inlineStr">
         <is>
-          <t>OCT250759</t>
+          <t>OCT251096</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -20964,7 +20952,7 @@
     <row r="761">
       <c r="B761" t="inlineStr">
         <is>
-          <t>OCT250760</t>
+          <t>OCT251097</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -20991,7 +20979,7 @@
     <row r="762">
       <c r="B762" t="inlineStr">
         <is>
-          <t>OCT250761</t>
+          <t>OCT251098</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -21018,7 +21006,7 @@
     <row r="763">
       <c r="B763" t="inlineStr">
         <is>
-          <t>OCT250762</t>
+          <t>OCT251099</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -21045,7 +21033,7 @@
     <row r="764">
       <c r="B764" t="inlineStr">
         <is>
-          <t>OCT250763</t>
+          <t>OCT251100</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -21072,7 +21060,7 @@
     <row r="765">
       <c r="B765" t="inlineStr">
         <is>
-          <t>OCT250764</t>
+          <t>OCT251101</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -21099,7 +21087,7 @@
     <row r="766">
       <c r="B766" t="inlineStr">
         <is>
-          <t>OCT250765</t>
+          <t>OCT251102</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -21126,7 +21114,7 @@
     <row r="767">
       <c r="B767" t="inlineStr">
         <is>
-          <t>OCT250766</t>
+          <t>OCT251103</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -21153,7 +21141,7 @@
     <row r="768">
       <c r="B768" t="inlineStr">
         <is>
-          <t>OCT250767</t>
+          <t>OCT251104</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -21180,7 +21168,7 @@
     <row r="769">
       <c r="B769" t="inlineStr">
         <is>
-          <t>OCT250768</t>
+          <t>OCT251105</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -21207,7 +21195,7 @@
     <row r="770">
       <c r="B770" t="inlineStr">
         <is>
-          <t>OCT250769</t>
+          <t>OCT251106</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -21234,7 +21222,7 @@
     <row r="771">
       <c r="B771" t="inlineStr">
         <is>
-          <t>OCT250770</t>
+          <t>OCT251107</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -21261,7 +21249,7 @@
     <row r="772">
       <c r="B772" t="inlineStr">
         <is>
-          <t>OCT250771</t>
+          <t>OCT251108</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -21288,7 +21276,7 @@
     <row r="773">
       <c r="B773" t="inlineStr">
         <is>
-          <t>OCT250772</t>
+          <t>OCT251109</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -21315,7 +21303,7 @@
     <row r="774">
       <c r="B774" t="inlineStr">
         <is>
-          <t>OCT250773</t>
+          <t>OCT251110</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -21342,7 +21330,7 @@
     <row r="775">
       <c r="B775" t="inlineStr">
         <is>
-          <t>OCT250774</t>
+          <t>OCT251111</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -21369,7 +21357,7 @@
     <row r="776">
       <c r="B776" t="inlineStr">
         <is>
-          <t>OCT250775</t>
+          <t>OCT251112</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -21396,7 +21384,7 @@
     <row r="777">
       <c r="B777" t="inlineStr">
         <is>
-          <t>OCT250776</t>
+          <t>OCT251113</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -21423,7 +21411,7 @@
     <row r="778">
       <c r="B778" t="inlineStr">
         <is>
-          <t>OCT250777</t>
+          <t>OCT251114</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -21450,7 +21438,7 @@
     <row r="779">
       <c r="B779" t="inlineStr">
         <is>
-          <t>OCT250778</t>
+          <t>OCT251115</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -21477,7 +21465,7 @@
     <row r="780">
       <c r="B780" t="inlineStr">
         <is>
-          <t>OCT250779</t>
+          <t>OCT251116</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -21504,7 +21492,7 @@
     <row r="781">
       <c r="B781" t="inlineStr">
         <is>
-          <t>OCT250780</t>
+          <t>OCT251117</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -21531,7 +21519,7 @@
     <row r="782">
       <c r="B782" t="inlineStr">
         <is>
-          <t>OCT250781</t>
+          <t>OCT251118</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -21558,7 +21546,7 @@
     <row r="783">
       <c r="B783" t="inlineStr">
         <is>
-          <t>OCT250782</t>
+          <t>OCT251119</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -21585,7 +21573,7 @@
     <row r="784">
       <c r="B784" t="inlineStr">
         <is>
-          <t>OCT250783</t>
+          <t>OCT251120</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -21612,7 +21600,7 @@
     <row r="785">
       <c r="B785" t="inlineStr">
         <is>
-          <t>OCT250784</t>
+          <t>OCT251121</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -21639,7 +21627,7 @@
     <row r="786">
       <c r="B786" t="inlineStr">
         <is>
-          <t>OCT250785</t>
+          <t>OCT251122</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -21666,7 +21654,7 @@
     <row r="787">
       <c r="B787" t="inlineStr">
         <is>
-          <t>OCT250786</t>
+          <t>OCT251123</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -21693,7 +21681,7 @@
     <row r="788">
       <c r="B788" t="inlineStr">
         <is>
-          <t>OCT250787</t>
+          <t>OCT251124</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -21720,7 +21708,7 @@
     <row r="789">
       <c r="B789" t="inlineStr">
         <is>
-          <t>OCT250788</t>
+          <t>OCT251125</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -21747,7 +21735,7 @@
     <row r="790">
       <c r="B790" t="inlineStr">
         <is>
-          <t>OCT250789</t>
+          <t>OCT251126</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -21774,7 +21762,7 @@
     <row r="791">
       <c r="B791" t="inlineStr">
         <is>
-          <t>OCT250790</t>
+          <t>OCT251127</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -21801,7 +21789,7 @@
     <row r="792">
       <c r="B792" t="inlineStr">
         <is>
-          <t>OCT250791</t>
+          <t>OCT251128</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -21828,7 +21816,7 @@
     <row r="793">
       <c r="B793" t="inlineStr">
         <is>
-          <t>OCT250792</t>
+          <t>OCT251129</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -21855,7 +21843,7 @@
     <row r="794">
       <c r="B794" t="inlineStr">
         <is>
-          <t>OCT250793</t>
+          <t>OCT251130</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -21882,7 +21870,7 @@
     <row r="795">
       <c r="B795" t="inlineStr">
         <is>
-          <t>OCT250794</t>
+          <t>OCT251131</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -21909,7 +21897,7 @@
     <row r="796">
       <c r="B796" t="inlineStr">
         <is>
-          <t>OCT250795</t>
+          <t>OCT251132</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -21936,7 +21924,7 @@
     <row r="797">
       <c r="B797" t="inlineStr">
         <is>
-          <t>OCT250796</t>
+          <t>OCT251133</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -21963,7 +21951,7 @@
     <row r="798">
       <c r="B798" t="inlineStr">
         <is>
-          <t>OCT250797</t>
+          <t>OCT251134</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -21990,7 +21978,7 @@
     <row r="799">
       <c r="B799" t="inlineStr">
         <is>
-          <t>OCT250798</t>
+          <t>OCT251135</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -22017,7 +22005,7 @@
     <row r="800">
       <c r="B800" t="inlineStr">
         <is>
-          <t>OCT250799</t>
+          <t>OCT251136</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -22044,7 +22032,7 @@
     <row r="801">
       <c r="B801" t="inlineStr">
         <is>
-          <t>OCT250800</t>
+          <t>OCT251137</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -22071,7 +22059,7 @@
     <row r="802">
       <c r="B802" t="inlineStr">
         <is>
-          <t>OCT250801</t>
+          <t>OCT251138</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -22098,7 +22086,7 @@
     <row r="803">
       <c r="B803" t="inlineStr">
         <is>
-          <t>OCT250802</t>
+          <t>OCT251139</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -22125,7 +22113,7 @@
     <row r="804">
       <c r="B804" t="inlineStr">
         <is>
-          <t>OCT250803</t>
+          <t>OCT251140</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -22152,7 +22140,7 @@
     <row r="805">
       <c r="B805" t="inlineStr">
         <is>
-          <t>OCT250804</t>
+          <t>OCT251141</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -22179,7 +22167,7 @@
     <row r="806">
       <c r="B806" t="inlineStr">
         <is>
-          <t>OCT250805</t>
+          <t>OCT251142</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -22206,7 +22194,7 @@
     <row r="807">
       <c r="B807" t="inlineStr">
         <is>
-          <t>OCT250806</t>
+          <t>OCT251143</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -22233,7 +22221,7 @@
     <row r="808">
       <c r="B808" t="inlineStr">
         <is>
-          <t>OCT250807</t>
+          <t>OCT251144</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -22260,7 +22248,7 @@
     <row r="809">
       <c r="B809" t="inlineStr">
         <is>
-          <t>OCT250808</t>
+          <t>OCT251145</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -22287,7 +22275,7 @@
     <row r="810">
       <c r="B810" t="inlineStr">
         <is>
-          <t>OCT250809</t>
+          <t>OCT251146</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -22314,7 +22302,7 @@
     <row r="811">
       <c r="B811" t="inlineStr">
         <is>
-          <t>OCT250810</t>
+          <t>OCT251147</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -22341,7 +22329,7 @@
     <row r="812">
       <c r="B812" t="inlineStr">
         <is>
-          <t>OCT250811</t>
+          <t>OCT251148</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -22368,7 +22356,7 @@
     <row r="813">
       <c r="B813" t="inlineStr">
         <is>
-          <t>OCT250812</t>
+          <t>OCT251149</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -22395,7 +22383,7 @@
     <row r="814">
       <c r="B814" t="inlineStr">
         <is>
-          <t>OCT250813</t>
+          <t>OCT251150</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -22422,7 +22410,7 @@
     <row r="815">
       <c r="B815" t="inlineStr">
         <is>
-          <t>OCT250814</t>
+          <t>OCT251151</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -22449,7 +22437,7 @@
     <row r="816">
       <c r="B816" t="inlineStr">
         <is>
-          <t>OCT250815</t>
+          <t>OCT251152</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -22476,7 +22464,7 @@
     <row r="817">
       <c r="B817" t="inlineStr">
         <is>
-          <t>OCT250816</t>
+          <t>OCT251153</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -22503,7 +22491,7 @@
     <row r="818">
       <c r="B818" t="inlineStr">
         <is>
-          <t>OCT250817</t>
+          <t>OCT251154</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -22530,7 +22518,7 @@
     <row r="819">
       <c r="B819" t="inlineStr">
         <is>
-          <t>OCT250818</t>
+          <t>OCT251155</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -22557,7 +22545,7 @@
     <row r="820">
       <c r="B820" t="inlineStr">
         <is>
-          <t>OCT250819</t>
+          <t>OCT251156</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -22584,7 +22572,7 @@
     <row r="821">
       <c r="B821" t="inlineStr">
         <is>
-          <t>OCT250820</t>
+          <t>OCT251157</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -22611,7 +22599,7 @@
     <row r="822">
       <c r="B822" t="inlineStr">
         <is>
-          <t>OCT250821</t>
+          <t>OCT251158</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -22638,7 +22626,7 @@
     <row r="823">
       <c r="B823" t="inlineStr">
         <is>
-          <t>OCT250822</t>
+          <t>OCT251159</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -22665,7 +22653,7 @@
     <row r="824">
       <c r="B824" t="inlineStr">
         <is>
-          <t>OCT250823</t>
+          <t>OCT251160</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -22692,7 +22680,7 @@
     <row r="825">
       <c r="B825" t="inlineStr">
         <is>
-          <t>OCT250824</t>
+          <t>OCT251161</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -22719,7 +22707,7 @@
     <row r="826">
       <c r="B826" t="inlineStr">
         <is>
-          <t>OCT250825</t>
+          <t>OCT251162</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -22746,7 +22734,7 @@
     <row r="827">
       <c r="B827" t="inlineStr">
         <is>
-          <t>OCT250826</t>
+          <t>OCT251163</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -22773,7 +22761,7 @@
     <row r="828">
       <c r="B828" t="inlineStr">
         <is>
-          <t>OCT250827</t>
+          <t>OCT251164</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -22800,7 +22788,7 @@
     <row r="829">
       <c r="B829" t="inlineStr">
         <is>
-          <t>OCT250828</t>
+          <t>OCT251165</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -22827,7 +22815,7 @@
     <row r="830">
       <c r="B830" t="inlineStr">
         <is>
-          <t>OCT250829</t>
+          <t>OCT251166</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -22854,7 +22842,7 @@
     <row r="831">
       <c r="B831" t="inlineStr">
         <is>
-          <t>OCT250830</t>
+          <t>OCT251167</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -22881,7 +22869,7 @@
     <row r="832">
       <c r="B832" t="inlineStr">
         <is>
-          <t>OCT250831</t>
+          <t>OCT251168</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -22908,7 +22896,7 @@
     <row r="833">
       <c r="B833" t="inlineStr">
         <is>
-          <t>OCT250832</t>
+          <t>OCT251169</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -22935,7 +22923,7 @@
     <row r="834">
       <c r="B834" t="inlineStr">
         <is>
-          <t>OCT250833</t>
+          <t>OCT251170</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -22962,7 +22950,7 @@
     <row r="835">
       <c r="B835" t="inlineStr">
         <is>
-          <t>OCT250834</t>
+          <t>OCT251171</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -22989,7 +22977,7 @@
     <row r="836">
       <c r="B836" t="inlineStr">
         <is>
-          <t>OCT250835</t>
+          <t>OCT251172</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -23016,7 +23004,7 @@
     <row r="837">
       <c r="B837" t="inlineStr">
         <is>
-          <t>OCT250836</t>
+          <t>OCT251173</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -23043,7 +23031,7 @@
     <row r="838">
       <c r="B838" t="inlineStr">
         <is>
-          <t>OCT250837</t>
+          <t>OCT251174</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -23070,7 +23058,7 @@
     <row r="839">
       <c r="B839" t="inlineStr">
         <is>
-          <t>OCT250838</t>
+          <t>OCT251175</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -23097,7 +23085,7 @@
     <row r="840">
       <c r="B840" t="inlineStr">
         <is>
-          <t>OCT250839</t>
+          <t>OCT251176</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -23124,7 +23112,7 @@
     <row r="841">
       <c r="B841" t="inlineStr">
         <is>
-          <t>OCT250840</t>
+          <t>OCT251177</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -23151,7 +23139,7 @@
     <row r="842">
       <c r="B842" t="inlineStr">
         <is>
-          <t>OCT250841</t>
+          <t>OCT251178</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -23178,7 +23166,7 @@
     <row r="843">
       <c r="B843" t="inlineStr">
         <is>
-          <t>OCT250842</t>
+          <t>OCT251179</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -23205,7 +23193,7 @@
     <row r="844">
       <c r="B844" t="inlineStr">
         <is>
-          <t>OCT250843</t>
+          <t>OCT251180</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -23232,7 +23220,7 @@
     <row r="845">
       <c r="B845" t="inlineStr">
         <is>
-          <t>OCT250844</t>
+          <t>OCT251181</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -23259,7 +23247,7 @@
     <row r="846">
       <c r="B846" t="inlineStr">
         <is>
-          <t>OCT250845</t>
+          <t>OCT251182</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -23286,7 +23274,7 @@
     <row r="847">
       <c r="B847" t="inlineStr">
         <is>
-          <t>OCT250846</t>
+          <t>OCT251183</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -23313,7 +23301,7 @@
     <row r="848">
       <c r="B848" t="inlineStr">
         <is>
-          <t>OCT250847</t>
+          <t>OCT251184</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -23340,7 +23328,7 @@
     <row r="849">
       <c r="B849" t="inlineStr">
         <is>
-          <t>OCT250848</t>
+          <t>OCT251185</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -23367,7 +23355,7 @@
     <row r="850">
       <c r="B850" t="inlineStr">
         <is>
-          <t>OCT250849</t>
+          <t>OCT251186</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -23394,7 +23382,7 @@
     <row r="851">
       <c r="B851" t="inlineStr">
         <is>
-          <t>OCT250850</t>
+          <t>OCT251187</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -23421,7 +23409,7 @@
     <row r="852">
       <c r="B852" t="inlineStr">
         <is>
-          <t>OCT250851</t>
+          <t>OCT251188</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -23448,7 +23436,7 @@
     <row r="853">
       <c r="B853" t="inlineStr">
         <is>
-          <t>OCT250852</t>
+          <t>OCT251189</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -23475,7 +23463,7 @@
     <row r="854">
       <c r="B854" t="inlineStr">
         <is>
-          <t>OCT250853</t>
+          <t>OCT251190</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -23502,7 +23490,7 @@
     <row r="855">
       <c r="B855" t="inlineStr">
         <is>
-          <t>OCT250854</t>
+          <t>OCT251191</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -23529,7 +23517,7 @@
     <row r="856">
       <c r="B856" t="inlineStr">
         <is>
-          <t>OCT250855</t>
+          <t>OCT251192</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -23556,7 +23544,7 @@
     <row r="857">
       <c r="B857" t="inlineStr">
         <is>
-          <t>OCT250856</t>
+          <t>OCT251193</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -23583,7 +23571,7 @@
     <row r="858">
       <c r="B858" t="inlineStr">
         <is>
-          <t>OCT250857</t>
+          <t>OCT251194</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -23610,7 +23598,7 @@
     <row r="859">
       <c r="B859" t="inlineStr">
         <is>
-          <t>OCT250858</t>
+          <t>OCT251195</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -23637,7 +23625,7 @@
     <row r="860">
       <c r="B860" t="inlineStr">
         <is>
-          <t>OCT250859</t>
+          <t>OCT251196</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -23664,7 +23652,7 @@
     <row r="861">
       <c r="B861" t="inlineStr">
         <is>
-          <t>OCT250860</t>
+          <t>OCT251197</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -23691,7 +23679,7 @@
     <row r="862">
       <c r="B862" t="inlineStr">
         <is>
-          <t>OCT250861</t>
+          <t>OCT251198</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -23718,7 +23706,7 @@
     <row r="863">
       <c r="B863" t="inlineStr">
         <is>
-          <t>OCT250862</t>
+          <t>OCT251199</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -23745,7 +23733,7 @@
     <row r="864">
       <c r="B864" t="inlineStr">
         <is>
-          <t>OCT250863</t>
+          <t>OCT251200</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -23772,7 +23760,7 @@
     <row r="865">
       <c r="B865" t="inlineStr">
         <is>
-          <t>OCT250864</t>
+          <t>OCT251201</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -23799,7 +23787,7 @@
     <row r="866">
       <c r="B866" t="inlineStr">
         <is>
-          <t>OCT250865</t>
+          <t>OCT251202</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -23826,7 +23814,7 @@
     <row r="867">
       <c r="B867" t="inlineStr">
         <is>
-          <t>OCT250866</t>
+          <t>OCT251203</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -23853,7 +23841,7 @@
     <row r="868">
       <c r="B868" t="inlineStr">
         <is>
-          <t>OCT250867</t>
+          <t>OCT251204</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -23880,7 +23868,7 @@
     <row r="869">
       <c r="B869" t="inlineStr">
         <is>
-          <t>OCT250868</t>
+          <t>OCT251205</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -23907,7 +23895,7 @@
     <row r="870">
       <c r="B870" t="inlineStr">
         <is>
-          <t>OCT250869</t>
+          <t>OCT251206</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -23934,7 +23922,7 @@
     <row r="871">
       <c r="B871" t="inlineStr">
         <is>
-          <t>OCT250870</t>
+          <t>OCT251207</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -23961,7 +23949,7 @@
     <row r="872">
       <c r="B872" t="inlineStr">
         <is>
-          <t>OCT250871</t>
+          <t>OCT251208</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -23988,7 +23976,7 @@
     <row r="873">
       <c r="B873" t="inlineStr">
         <is>
-          <t>OCT250872</t>
+          <t>OCT251209</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -24015,7 +24003,7 @@
     <row r="874">
       <c r="B874" t="inlineStr">
         <is>
-          <t>OCT250873</t>
+          <t>OCT251210</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -24042,7 +24030,7 @@
     <row r="875">
       <c r="B875" t="inlineStr">
         <is>
-          <t>OCT250874</t>
+          <t>OCT251211</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -24069,7 +24057,7 @@
     <row r="876">
       <c r="B876" t="inlineStr">
         <is>
-          <t>OCT250875</t>
+          <t>OCT251212</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -24096,7 +24084,7 @@
     <row r="877">
       <c r="B877" t="inlineStr">
         <is>
-          <t>OCT250876</t>
+          <t>OCT251213</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -24123,7 +24111,7 @@
     <row r="878">
       <c r="B878" t="inlineStr">
         <is>
-          <t>OCT250877</t>
+          <t>OCT251214</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -24150,7 +24138,7 @@
     <row r="879">
       <c r="B879" t="inlineStr">
         <is>
-          <t>OCT250878</t>
+          <t>OCT251215</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -24177,7 +24165,7 @@
     <row r="880">
       <c r="B880" t="inlineStr">
         <is>
-          <t>OCT250879</t>
+          <t>OCT251216</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -24204,7 +24192,7 @@
     <row r="881">
       <c r="B881" t="inlineStr">
         <is>
-          <t>OCT250880</t>
+          <t>OCT251217</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -24231,7 +24219,7 @@
     <row r="882">
       <c r="B882" t="inlineStr">
         <is>
-          <t>OCT250881</t>
+          <t>OCT251218</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -24258,7 +24246,7 @@
     <row r="883">
       <c r="B883" t="inlineStr">
         <is>
-          <t>OCT250882</t>
+          <t>OCT251219</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -24285,7 +24273,7 @@
     <row r="884">
       <c r="B884" t="inlineStr">
         <is>
-          <t>OCT250883</t>
+          <t>OCT251220</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -24312,7 +24300,7 @@
     <row r="885">
       <c r="B885" t="inlineStr">
         <is>
-          <t>OCT250884</t>
+          <t>OCT251221</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -24339,7 +24327,7 @@
     <row r="886">
       <c r="B886" t="inlineStr">
         <is>
-          <t>OCT250885</t>
+          <t>OCT251222</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -24366,7 +24354,7 @@
     <row r="887">
       <c r="B887" t="inlineStr">
         <is>
-          <t>OCT250886</t>
+          <t>OCT251223</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -24393,7 +24381,7 @@
     <row r="888">
       <c r="B888" t="inlineStr">
         <is>
-          <t>OCT250887</t>
+          <t>OCT251224</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -24420,7 +24408,7 @@
     <row r="889">
       <c r="B889" t="inlineStr">
         <is>
-          <t>OCT250888</t>
+          <t>OCT251225</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -24447,7 +24435,7 @@
     <row r="890">
       <c r="B890" t="inlineStr">
         <is>
-          <t>OCT250889</t>
+          <t>OCT251226</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -24474,7 +24462,7 @@
     <row r="891">
       <c r="B891" t="inlineStr">
         <is>
-          <t>OCT250890</t>
+          <t>OCT251227</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -24501,7 +24489,7 @@
     <row r="892">
       <c r="B892" t="inlineStr">
         <is>
-          <t>OCT250891</t>
+          <t>OCT251228</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -24528,7 +24516,7 @@
     <row r="893">
       <c r="B893" t="inlineStr">
         <is>
-          <t>OCT250892</t>
+          <t>OCT251229</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -24555,7 +24543,7 @@
     <row r="894">
       <c r="B894" t="inlineStr">
         <is>
-          <t>OCT250893</t>
+          <t>OCT251230</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -24582,7 +24570,7 @@
     <row r="895">
       <c r="B895" t="inlineStr">
         <is>
-          <t>OCT250894</t>
+          <t>OCT251231</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -24609,7 +24597,7 @@
     <row r="896">
       <c r="B896" t="inlineStr">
         <is>
-          <t>OCT250895</t>
+          <t>OCT251232</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -24636,7 +24624,7 @@
     <row r="897">
       <c r="B897" t="inlineStr">
         <is>
-          <t>OCT250896</t>
+          <t>OCT251233</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -24663,7 +24651,7 @@
     <row r="898">
       <c r="B898" t="inlineStr">
         <is>
-          <t>OCT250897</t>
+          <t>OCT251234</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -24690,7 +24678,7 @@
     <row r="899">
       <c r="B899" t="inlineStr">
         <is>
-          <t>OCT250898</t>
+          <t>OCT251235</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -24717,7 +24705,7 @@
     <row r="900">
       <c r="B900" t="inlineStr">
         <is>
-          <t>OCT250899</t>
+          <t>OCT251236</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -24744,7 +24732,7 @@
     <row r="901">
       <c r="B901" t="inlineStr">
         <is>
-          <t>OCT250900</t>
+          <t>OCT251237</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -24771,7 +24759,7 @@
     <row r="902">
       <c r="B902" t="inlineStr">
         <is>
-          <t>OCT250901</t>
+          <t>OCT251238</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -24798,7 +24786,7 @@
     <row r="903">
       <c r="B903" t="inlineStr">
         <is>
-          <t>OCT250902</t>
+          <t>OCT251239</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -24825,7 +24813,7 @@
     <row r="904">
       <c r="B904" t="inlineStr">
         <is>
-          <t>OCT250903</t>
+          <t>OCT251240</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -24852,7 +24840,7 @@
     <row r="905">
       <c r="B905" t="inlineStr">
         <is>
-          <t>OCT250904</t>
+          <t>OCT251241</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -24879,7 +24867,7 @@
     <row r="906">
       <c r="B906" t="inlineStr">
         <is>
-          <t>OCT250905</t>
+          <t>OCT251242</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -24906,7 +24894,7 @@
     <row r="907">
       <c r="B907" t="inlineStr">
         <is>
-          <t>OCT250906</t>
+          <t>OCT251243</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -24933,7 +24921,7 @@
     <row r="908">
       <c r="B908" t="inlineStr">
         <is>
-          <t>OCT250907</t>
+          <t>OCT251244</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -24960,7 +24948,7 @@
     <row r="909">
       <c r="B909" t="inlineStr">
         <is>
-          <t>OCT250908</t>
+          <t>OCT251245</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -24987,7 +24975,7 @@
     <row r="910">
       <c r="B910" t="inlineStr">
         <is>
-          <t>OCT250909</t>
+          <t>OCT251246</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -25014,7 +25002,7 @@
     <row r="911">
       <c r="B911" t="inlineStr">
         <is>
-          <t>OCT250910</t>
+          <t>OCT251247</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -25041,7 +25029,7 @@
     <row r="912">
       <c r="B912" t="inlineStr">
         <is>
-          <t>OCT250911</t>
+          <t>OCT251248</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -25068,7 +25056,7 @@
     <row r="913">
       <c r="B913" t="inlineStr">
         <is>
-          <t>OCT250912</t>
+          <t>OCT251249</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -25095,7 +25083,7 @@
     <row r="914">
       <c r="B914" t="inlineStr">
         <is>
-          <t>OCT250913</t>
+          <t>OCT251250</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -25122,7 +25110,7 @@
     <row r="915">
       <c r="B915" t="inlineStr">
         <is>
-          <t>OCT250914</t>
+          <t>OCT251251</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -25149,7 +25137,7 @@
     <row r="916">
       <c r="B916" t="inlineStr">
         <is>
-          <t>OCT250915</t>
+          <t>OCT251252</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -25176,7 +25164,7 @@
     <row r="917">
       <c r="B917" t="inlineStr">
         <is>
-          <t>OCT250916</t>
+          <t>OCT251253</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -25203,7 +25191,7 @@
     <row r="918">
       <c r="B918" t="inlineStr">
         <is>
-          <t>OCT250917</t>
+          <t>OCT251254</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -25230,7 +25218,7 @@
     <row r="919">
       <c r="B919" t="inlineStr">
         <is>
-          <t>OCT250918</t>
+          <t>OCT251255</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -25257,7 +25245,7 @@
     <row r="920">
       <c r="B920" t="inlineStr">
         <is>
-          <t>OCT250919</t>
+          <t>OCT251256</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -25284,7 +25272,7 @@
     <row r="921">
       <c r="B921" t="inlineStr">
         <is>
-          <t>OCT250920</t>
+          <t>OCT251257</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -25311,7 +25299,7 @@
     <row r="922">
       <c r="B922" t="inlineStr">
         <is>
-          <t>OCT250921</t>
+          <t>OCT251258</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -25338,7 +25326,7 @@
     <row r="923">
       <c r="B923" t="inlineStr">
         <is>
-          <t>OCT250922</t>
+          <t>OCT251259</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -25365,7 +25353,7 @@
     <row r="924">
       <c r="B924" t="inlineStr">
         <is>
-          <t>OCT250923</t>
+          <t>OCT251260</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -25392,7 +25380,7 @@
     <row r="925">
       <c r="B925" t="inlineStr">
         <is>
-          <t>OCT250924</t>
+          <t>OCT251261</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -25419,7 +25407,7 @@
     <row r="926">
       <c r="B926" t="inlineStr">
         <is>
-          <t>OCT250925</t>
+          <t>OCT251262</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -25446,7 +25434,7 @@
     <row r="927">
       <c r="B927" t="inlineStr">
         <is>
-          <t>OCT250926</t>
+          <t>OCT251263</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -25473,7 +25461,7 @@
     <row r="928">
       <c r="B928" t="inlineStr">
         <is>
-          <t>OCT250927</t>
+          <t>OCT251264</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -25500,7 +25488,7 @@
     <row r="929">
       <c r="B929" t="inlineStr">
         <is>
-          <t>OCT250928</t>
+          <t>OCT251265</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -25527,7 +25515,7 @@
     <row r="930">
       <c r="B930" t="inlineStr">
         <is>
-          <t>OCT250929</t>
+          <t>OCT251266</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -25554,7 +25542,7 @@
     <row r="931">
       <c r="B931" t="inlineStr">
         <is>
-          <t>OCT250930</t>
+          <t>OCT251267</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -25581,7 +25569,7 @@
     <row r="932">
       <c r="B932" t="inlineStr">
         <is>
-          <t>OCT250931</t>
+          <t>OCT251268</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -25608,7 +25596,7 @@
     <row r="933">
       <c r="B933" t="inlineStr">
         <is>
-          <t>OCT250932</t>
+          <t>OCT251269</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -25635,7 +25623,7 @@
     <row r="934">
       <c r="B934" t="inlineStr">
         <is>
-          <t>OCT250933</t>
+          <t>OCT251270</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -25662,7 +25650,7 @@
     <row r="935">
       <c r="B935" t="inlineStr">
         <is>
-          <t>OCT250934</t>
+          <t>OCT251271</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -25689,7 +25677,7 @@
     <row r="936">
       <c r="B936" t="inlineStr">
         <is>
-          <t>OCT250935</t>
+          <t>OCT251272</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -25716,7 +25704,7 @@
     <row r="937">
       <c r="B937" t="inlineStr">
         <is>
-          <t>OCT250936</t>
+          <t>OCT251273</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -25743,7 +25731,7 @@
     <row r="938">
       <c r="B938" t="inlineStr">
         <is>
-          <t>OCT250937</t>
+          <t>OCT251274</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -25770,7 +25758,7 @@
     <row r="939">
       <c r="B939" t="inlineStr">
         <is>
-          <t>OCT250938</t>
+          <t>OCT251275</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -25797,7 +25785,7 @@
     <row r="940">
       <c r="B940" t="inlineStr">
         <is>
-          <t>OCT250939</t>
+          <t>OCT251276</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -25824,7 +25812,7 @@
     <row r="941">
       <c r="B941" t="inlineStr">
         <is>
-          <t>OCT250940</t>
+          <t>OCT251277</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -25851,7 +25839,7 @@
     <row r="942">
       <c r="B942" t="inlineStr">
         <is>
-          <t>OCT250941</t>
+          <t>OCT251278</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -25878,7 +25866,7 @@
     <row r="943">
       <c r="B943" t="inlineStr">
         <is>
-          <t>OCT250942</t>
+          <t>OCT251279</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -25905,7 +25893,7 @@
     <row r="944">
       <c r="B944" t="inlineStr">
         <is>
-          <t>OCT250943</t>
+          <t>OCT251280</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -25932,7 +25920,7 @@
     <row r="945">
       <c r="B945" t="inlineStr">
         <is>
-          <t>OCT250944</t>
+          <t>OCT251281</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -25959,7 +25947,7 @@
     <row r="946">
       <c r="B946" t="inlineStr">
         <is>
-          <t>OCT250945</t>
+          <t>OCT251282</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -25986,7 +25974,7 @@
     <row r="947">
       <c r="B947" t="inlineStr">
         <is>
-          <t>OCT250946</t>
+          <t>OCT251283</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -26013,7 +26001,7 @@
     <row r="948">
       <c r="B948" t="inlineStr">
         <is>
-          <t>OCT250947</t>
+          <t>OCT251284</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
@@ -26040,7 +26028,7 @@
     <row r="949">
       <c r="B949" t="inlineStr">
         <is>
-          <t>OCT250948</t>
+          <t>OCT251285</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -26067,7 +26055,7 @@
     <row r="950">
       <c r="B950" t="inlineStr">
         <is>
-          <t>OCT250949</t>
+          <t>OCT251286</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -26094,7 +26082,7 @@
     <row r="951">
       <c r="B951" t="inlineStr">
         <is>
-          <t>OCT250950</t>
+          <t>OCT251287</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -26121,7 +26109,7 @@
     <row r="952">
       <c r="B952" t="inlineStr">
         <is>
-          <t>OCT250951</t>
+          <t>OCT251288</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -26148,7 +26136,7 @@
     <row r="953">
       <c r="B953" t="inlineStr">
         <is>
-          <t>OCT250952</t>
+          <t>OCT251289</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -26175,7 +26163,7 @@
     <row r="954">
       <c r="B954" t="inlineStr">
         <is>
-          <t>OCT250953</t>
+          <t>OCT251290</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -26202,7 +26190,7 @@
     <row r="955">
       <c r="B955" t="inlineStr">
         <is>
-          <t>OCT250954</t>
+          <t>OCT251291</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -26229,7 +26217,7 @@
     <row r="956">
       <c r="B956" t="inlineStr">
         <is>
-          <t>OCT250955</t>
+          <t>OCT251292</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -26256,7 +26244,7 @@
     <row r="957">
       <c r="B957" t="inlineStr">
         <is>
-          <t>OCT250956</t>
+          <t>OCT251293</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -26283,7 +26271,7 @@
     <row r="958">
       <c r="B958" t="inlineStr">
         <is>
-          <t>OCT250957</t>
+          <t>OCT251294</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -26310,7 +26298,7 @@
     <row r="959">
       <c r="B959" t="inlineStr">
         <is>
-          <t>OCT250958</t>
+          <t>OCT251295</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -26337,7 +26325,7 @@
     <row r="960">
       <c r="B960" t="inlineStr">
         <is>
-          <t>OCT250959</t>
+          <t>OCT251296</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -26364,7 +26352,7 @@
     <row r="961">
       <c r="B961" t="inlineStr">
         <is>
-          <t>OCT250960</t>
+          <t>OCT251297</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -26391,7 +26379,7 @@
     <row r="962">
       <c r="B962" t="inlineStr">
         <is>
-          <t>OCT250961</t>
+          <t>OCT251298</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -26418,7 +26406,7 @@
     <row r="963">
       <c r="B963" t="inlineStr">
         <is>
-          <t>OCT250962</t>
+          <t>OCT251299</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -26445,7 +26433,7 @@
     <row r="964">
       <c r="B964" t="inlineStr">
         <is>
-          <t>OCT250963</t>
+          <t>OCT251300</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -26472,7 +26460,7 @@
     <row r="965">
       <c r="B965" t="inlineStr">
         <is>
-          <t>OCT250964</t>
+          <t>OCT251301</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -26499,7 +26487,7 @@
     <row r="966">
       <c r="B966" t="inlineStr">
         <is>
-          <t>OCT250965</t>
+          <t>OCT251302</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -26526,7 +26514,7 @@
     <row r="967">
       <c r="B967" t="inlineStr">
         <is>
-          <t>OCT250966</t>
+          <t>OCT251303</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -26553,7 +26541,7 @@
     <row r="968">
       <c r="B968" t="inlineStr">
         <is>
-          <t>OCT250967</t>
+          <t>OCT251304</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -26580,7 +26568,7 @@
     <row r="969">
       <c r="B969" t="inlineStr">
         <is>
-          <t>OCT250968</t>
+          <t>OCT251305</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -26607,7 +26595,7 @@
     <row r="970">
       <c r="B970" t="inlineStr">
         <is>
-          <t>OCT250969</t>
+          <t>OCT251306</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -26634,7 +26622,7 @@
     <row r="971">
       <c r="B971" t="inlineStr">
         <is>
-          <t>OCT250970</t>
+          <t>OCT251307</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -26661,7 +26649,7 @@
     <row r="972">
       <c r="B972" t="inlineStr">
         <is>
-          <t>OCT250971</t>
+          <t>OCT251308</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -26688,7 +26676,7 @@
     <row r="973">
       <c r="B973" t="inlineStr">
         <is>
-          <t>OCT250972</t>
+          <t>OCT251309</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -26715,7 +26703,7 @@
     <row r="974">
       <c r="B974" t="inlineStr">
         <is>
-          <t>OCT250973</t>
+          <t>OCT251310</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -26742,7 +26730,7 @@
     <row r="975">
       <c r="B975" t="inlineStr">
         <is>
-          <t>OCT250974</t>
+          <t>OCT251311</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -26769,7 +26757,7 @@
     <row r="976">
       <c r="B976" t="inlineStr">
         <is>
-          <t>OCT250975</t>
+          <t>OCT251312</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -26796,7 +26784,7 @@
     <row r="977">
       <c r="B977" t="inlineStr">
         <is>
-          <t>OCT250976</t>
+          <t>OCT251313</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -26823,7 +26811,7 @@
     <row r="978">
       <c r="B978" t="inlineStr">
         <is>
-          <t>OCT250977</t>
+          <t>OCT251314</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -26850,7 +26838,7 @@
     <row r="979">
       <c r="B979" t="inlineStr">
         <is>
-          <t>OCT250978</t>
+          <t>OCT251315</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -26877,7 +26865,7 @@
     <row r="980">
       <c r="B980" t="inlineStr">
         <is>
-          <t>OCT250979</t>
+          <t>OCT251316</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -26904,7 +26892,7 @@
     <row r="981">
       <c r="B981" t="inlineStr">
         <is>
-          <t>OCT250980</t>
+          <t>OCT251317</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -26931,7 +26919,7 @@
     <row r="982">
       <c r="B982" t="inlineStr">
         <is>
-          <t>OCT250981</t>
+          <t>OCT251318</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -26958,7 +26946,7 @@
     <row r="983">
       <c r="B983" t="inlineStr">
         <is>
-          <t>OCT250982</t>
+          <t>OCT251319</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -26985,7 +26973,7 @@
     <row r="984">
       <c r="B984" t="inlineStr">
         <is>
-          <t>OCT250983</t>
+          <t>OCT251320</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -27012,7 +27000,7 @@
     <row r="985">
       <c r="B985" t="inlineStr">
         <is>
-          <t>OCT250984</t>
+          <t>OCT251321</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -27039,7 +27027,7 @@
     <row r="986">
       <c r="B986" t="inlineStr">
         <is>
-          <t>OCT250985</t>
+          <t>OCT251322</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -27066,7 +27054,7 @@
     <row r="987">
       <c r="B987" t="inlineStr">
         <is>
-          <t>OCT250986</t>
+          <t>OCT251323</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -27093,7 +27081,7 @@
     <row r="988">
       <c r="B988" t="inlineStr">
         <is>
-          <t>OCT250987</t>
+          <t>OCT251324</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -27120,7 +27108,7 @@
     <row r="989">
       <c r="B989" t="inlineStr">
         <is>
-          <t>OCT250988</t>
+          <t>OCT251325</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -27147,7 +27135,7 @@
     <row r="990">
       <c r="B990" t="inlineStr">
         <is>
-          <t>OCT250989</t>
+          <t>OCT251326</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -27174,7 +27162,7 @@
     <row r="991">
       <c r="B991" t="inlineStr">
         <is>
-          <t>OCT250990</t>
+          <t>OCT251327</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -27201,7 +27189,7 @@
     <row r="992">
       <c r="B992" t="inlineStr">
         <is>
-          <t>OCT250991</t>
+          <t>OCT251328</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -27228,7 +27216,7 @@
     <row r="993">
       <c r="B993" t="inlineStr">
         <is>
-          <t>OCT250992</t>
+          <t>OCT251329</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -27255,7 +27243,7 @@
     <row r="994">
       <c r="B994" t="inlineStr">
         <is>
-          <t>OCT250993</t>
+          <t>OCT251330</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -27282,7 +27270,7 @@
     <row r="995">
       <c r="B995" t="inlineStr">
         <is>
-          <t>OCT250994</t>
+          <t>OCT251331</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -27309,7 +27297,7 @@
     <row r="996">
       <c r="B996" t="inlineStr">
         <is>
-          <t>OCT250995</t>
+          <t>OCT251332</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -27336,7 +27324,7 @@
     <row r="997">
       <c r="B997" t="inlineStr">
         <is>
-          <t>OCT250996</t>
+          <t>OCT251333</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -27363,7 +27351,7 @@
     <row r="998">
       <c r="B998" t="inlineStr">
         <is>
-          <t>OCT250997</t>
+          <t>OCT251334</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -27390,7 +27378,7 @@
     <row r="999">
       <c r="B999" t="inlineStr">
         <is>
-          <t>OCT250998</t>
+          <t>OCT251335</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -27417,7 +27405,7 @@
     <row r="1000">
       <c r="B1000" t="inlineStr">
         <is>
-          <t>OCT250999</t>
+          <t>OCT251336</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -27444,7 +27432,7 @@
     <row r="1001">
       <c r="B1001" t="inlineStr">
         <is>
-          <t>OCT251000</t>
+          <t>OCT251337</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -27471,7 +27459,7 @@
     <row r="1002">
       <c r="B1002" t="inlineStr">
         <is>
-          <t>OCT251001</t>
+          <t>OCT251338</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -27498,7 +27486,7 @@
     <row r="1003">
       <c r="B1003" t="inlineStr">
         <is>
-          <t>OCT251002</t>
+          <t>OCT251339</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -27525,7 +27513,7 @@
     <row r="1004">
       <c r="B1004" t="inlineStr">
         <is>
-          <t>OCT251003</t>
+          <t>OCT251340</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -27552,7 +27540,7 @@
     <row r="1005">
       <c r="B1005" t="inlineStr">
         <is>
-          <t>OCT251004</t>
+          <t>OCT251341</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -27579,7 +27567,7 @@
     <row r="1006">
       <c r="B1006" t="inlineStr">
         <is>
-          <t>OCT251005</t>
+          <t>OCT251342</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -27606,7 +27594,7 @@
     <row r="1007">
       <c r="B1007" t="inlineStr">
         <is>
-          <t>OCT251006</t>
+          <t>OCT251343</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -27633,7 +27621,7 @@
     <row r="1008">
       <c r="B1008" t="inlineStr">
         <is>
-          <t>OCT251007</t>
+          <t>OCT251344</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -27660,7 +27648,7 @@
     <row r="1009">
       <c r="B1009" t="inlineStr">
         <is>
-          <t>OCT251008</t>
+          <t>OCT251345</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -27687,7 +27675,7 @@
     <row r="1010">
       <c r="B1010" t="inlineStr">
         <is>
-          <t>OCT251009</t>
+          <t>OCT251346</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
@@ -27714,7 +27702,7 @@
     <row r="1011">
       <c r="B1011" t="inlineStr">
         <is>
-          <t>OCT251010</t>
+          <t>OCT251347</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -27741,7 +27729,7 @@
     <row r="1012">
       <c r="B1012" t="inlineStr">
         <is>
-          <t>OCT251011</t>
+          <t>OCT251348</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -27768,7 +27756,7 @@
     <row r="1013">
       <c r="B1013" t="inlineStr">
         <is>
-          <t>OCT251012</t>
+          <t>OCT251349</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -27795,7 +27783,7 @@
     <row r="1014">
       <c r="B1014" t="inlineStr">
         <is>
-          <t>OCT251013</t>
+          <t>OCT251350</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
@@ -27822,7 +27810,7 @@
     <row r="1015">
       <c r="B1015" t="inlineStr">
         <is>
-          <t>OCT251014</t>
+          <t>OCT251351</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -27849,7 +27837,7 @@
     <row r="1016">
       <c r="B1016" t="inlineStr">
         <is>
-          <t>OCT251015</t>
+          <t>OCT251352</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
@@ -27876,7 +27864,7 @@
     <row r="1017">
       <c r="B1017" t="inlineStr">
         <is>
-          <t>OCT251016</t>
+          <t>OCT251353</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -27903,7 +27891,7 @@
     <row r="1018">
       <c r="B1018" t="inlineStr">
         <is>
-          <t>OCT251017</t>
+          <t>OCT251354</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -27930,7 +27918,7 @@
     <row r="1019">
       <c r="B1019" t="inlineStr">
         <is>
-          <t>OCT251018</t>
+          <t>OCT251355</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -27957,7 +27945,7 @@
     <row r="1020">
       <c r="B1020" t="inlineStr">
         <is>
-          <t>OCT251019</t>
+          <t>OCT251356</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -27984,7 +27972,7 @@
     <row r="1021">
       <c r="B1021" t="inlineStr">
         <is>
-          <t>OCT251020</t>
+          <t>OCT251357</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -28011,7 +27999,7 @@
     <row r="1022">
       <c r="B1022" t="inlineStr">
         <is>
-          <t>OCT251021</t>
+          <t>OCT251358</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -28038,7 +28026,7 @@
     <row r="1023">
       <c r="B1023" t="inlineStr">
         <is>
-          <t>OCT251022</t>
+          <t>OCT251359</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -28065,7 +28053,7 @@
     <row r="1024">
       <c r="B1024" t="inlineStr">
         <is>
-          <t>OCT251023</t>
+          <t>OCT251360</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
@@ -28092,7 +28080,7 @@
     <row r="1025">
       <c r="B1025" t="inlineStr">
         <is>
-          <t>OCT251024</t>
+          <t>OCT251361</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -28119,7 +28107,7 @@
     <row r="1026">
       <c r="B1026" t="inlineStr">
         <is>
-          <t>OCT251025</t>
+          <t>OCT251362</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -28146,7 +28134,7 @@
     <row r="1027">
       <c r="B1027" t="inlineStr">
         <is>
-          <t>OCT251026</t>
+          <t>OCT251363</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -28173,7 +28161,7 @@
     <row r="1028">
       <c r="B1028" t="inlineStr">
         <is>
-          <t>OCT251027</t>
+          <t>OCT251364</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -28200,7 +28188,7 @@
     <row r="1029">
       <c r="B1029" t="inlineStr">
         <is>
-          <t>OCT251028</t>
+          <t>OCT251365</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -28227,7 +28215,7 @@
     <row r="1030">
       <c r="B1030" t="inlineStr">
         <is>
-          <t>OCT251029</t>
+          <t>OCT251366</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -28254,7 +28242,7 @@
     <row r="1031">
       <c r="B1031" t="inlineStr">
         <is>
-          <t>OCT251030</t>
+          <t>OCT251367</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -28281,7 +28269,7 @@
     <row r="1032">
       <c r="B1032" t="inlineStr">
         <is>
-          <t>OCT251031</t>
+          <t>OCT251368</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
@@ -28308,7 +28296,7 @@
     <row r="1033">
       <c r="B1033" t="inlineStr">
         <is>
-          <t>OCT251032</t>
+          <t>OCT251369</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -28335,7 +28323,7 @@
     <row r="1034">
       <c r="B1034" t="inlineStr">
         <is>
-          <t>OCT251033</t>
+          <t>OCT251370</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -28362,7 +28350,7 @@
     <row r="1035">
       <c r="B1035" t="inlineStr">
         <is>
-          <t>OCT251034</t>
+          <t>OCT251371</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -28389,7 +28377,7 @@
     <row r="1036">
       <c r="B1036" t="inlineStr">
         <is>
-          <t>OCT251035</t>
+          <t>OCT251372</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -28416,7 +28404,7 @@
     <row r="1037">
       <c r="B1037" t="inlineStr">
         <is>
-          <t>OCT251036</t>
+          <t>OCT251373</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -28443,7 +28431,7 @@
     <row r="1038">
       <c r="B1038" t="inlineStr">
         <is>
-          <t>OCT251037</t>
+          <t>OCT251374</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -28470,7 +28458,7 @@
     <row r="1039">
       <c r="B1039" t="inlineStr">
         <is>
-          <t>OCT251038</t>
+          <t>OCT251375</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -28497,7 +28485,7 @@
     <row r="1040">
       <c r="B1040" t="inlineStr">
         <is>
-          <t>OCT251039</t>
+          <t>OCT251376</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -28524,7 +28512,7 @@
     <row r="1041">
       <c r="B1041" t="inlineStr">
         <is>
-          <t>OCT251040</t>
+          <t>OCT251377</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
@@ -28551,7 +28539,7 @@
     <row r="1042">
       <c r="B1042" t="inlineStr">
         <is>
-          <t>OCT251041</t>
+          <t>OCT251378</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -28578,7 +28566,7 @@
     <row r="1043">
       <c r="B1043" t="inlineStr">
         <is>
-          <t>OCT251042</t>
+          <t>OCT251379</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -28605,7 +28593,7 @@
     <row r="1044">
       <c r="B1044" t="inlineStr">
         <is>
-          <t>OCT251043</t>
+          <t>OCT251380</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -28632,7 +28620,7 @@
     <row r="1045">
       <c r="B1045" t="inlineStr">
         <is>
-          <t>OCT251044</t>
+          <t>OCT251381</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -28659,7 +28647,7 @@
     <row r="1046">
       <c r="B1046" t="inlineStr">
         <is>
-          <t>OCT251045</t>
+          <t>OCT251382</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
@@ -28686,7 +28674,7 @@
     <row r="1047">
       <c r="B1047" t="inlineStr">
         <is>
-          <t>OCT251046</t>
+          <t>OCT251383</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -28713,7 +28701,7 @@
     <row r="1048">
       <c r="B1048" t="inlineStr">
         <is>
-          <t>OCT251047</t>
+          <t>OCT251384</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -28740,7 +28728,7 @@
     <row r="1049">
       <c r="B1049" t="inlineStr">
         <is>
-          <t>OCT251048</t>
+          <t>OCT251385</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -28767,7 +28755,7 @@
     <row r="1050">
       <c r="B1050" t="inlineStr">
         <is>
-          <t>OCT251049</t>
+          <t>OCT251386</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
@@ -28794,7 +28782,7 @@
     <row r="1051">
       <c r="B1051" t="inlineStr">
         <is>
-          <t>OCT251050</t>
+          <t>OCT251387</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -28821,7 +28809,7 @@
     <row r="1052">
       <c r="B1052" t="inlineStr">
         <is>
-          <t>OCT251051</t>
+          <t>OCT251388</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -28848,7 +28836,7 @@
     <row r="1053">
       <c r="B1053" t="inlineStr">
         <is>
-          <t>OCT251052</t>
+          <t>OCT251389</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -28875,7 +28863,7 @@
     <row r="1054">
       <c r="B1054" t="inlineStr">
         <is>
-          <t>OCT251053</t>
+          <t>OCT251390</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -28902,7 +28890,7 @@
     <row r="1055">
       <c r="B1055" t="inlineStr">
         <is>
-          <t>OCT251054</t>
+          <t>OCT251391</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -28929,7 +28917,7 @@
     <row r="1056">
       <c r="B1056" t="inlineStr">
         <is>
-          <t>OCT251055</t>
+          <t>OCT251392</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
@@ -28956,7 +28944,7 @@
     <row r="1057">
       <c r="B1057" t="inlineStr">
         <is>
-          <t>OCT251056</t>
+          <t>OCT251393</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -28983,7 +28971,7 @@
     <row r="1058">
       <c r="B1058" t="inlineStr">
         <is>
-          <t>OCT251057</t>
+          <t>OCT251394</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
@@ -29010,7 +28998,7 @@
     <row r="1059">
       <c r="B1059" t="inlineStr">
         <is>
-          <t>OCT251058</t>
+          <t>OCT251395</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -29037,7 +29025,7 @@
     <row r="1060">
       <c r="B1060" t="inlineStr">
         <is>
-          <t>OCT251059</t>
+          <t>OCT251396</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
@@ -29064,7 +29052,7 @@
     <row r="1061">
       <c r="B1061" t="inlineStr">
         <is>
-          <t>OCT251060</t>
+          <t>OCT251397</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -29091,7 +29079,7 @@
     <row r="1062">
       <c r="B1062" t="inlineStr">
         <is>
-          <t>OCT251061</t>
+          <t>OCT251398</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -29118,7 +29106,7 @@
     <row r="1063">
       <c r="B1063" t="inlineStr">
         <is>
-          <t>OCT251062</t>
+          <t>OCT251399</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -29145,7 +29133,7 @@
     <row r="1064">
       <c r="B1064" t="inlineStr">
         <is>
-          <t>OCT251063</t>
+          <t>OCT251400</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -29172,7 +29160,7 @@
     <row r="1065">
       <c r="B1065" t="inlineStr">
         <is>
-          <t>OCT251064</t>
+          <t>OCT251401</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -29199,7 +29187,7 @@
     <row r="1066">
       <c r="B1066" t="inlineStr">
         <is>
-          <t>OCT251065</t>
+          <t>OCT251402</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -29226,7 +29214,7 @@
     <row r="1067">
       <c r="B1067" t="inlineStr">
         <is>
-          <t>OCT251066</t>
+          <t>OCT251403</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -29253,7 +29241,7 @@
     <row r="1068">
       <c r="B1068" t="inlineStr">
         <is>
-          <t>OCT251067</t>
+          <t>OCT251404</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -29280,7 +29268,7 @@
     <row r="1069">
       <c r="B1069" t="inlineStr">
         <is>
-          <t>OCT251068</t>
+          <t>OCT251405</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -29307,7 +29295,7 @@
     <row r="1070">
       <c r="B1070" t="inlineStr">
         <is>
-          <t>OCT251069</t>
+          <t>OCT251406</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -29334,7 +29322,7 @@
     <row r="1071">
       <c r="B1071" t="inlineStr">
         <is>
-          <t>OCT251070</t>
+          <t>OCT251407</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -29361,7 +29349,7 @@
     <row r="1072">
       <c r="B1072" t="inlineStr">
         <is>
-          <t>OCT251071</t>
+          <t>OCT251408</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -29388,7 +29376,7 @@
     <row r="1073">
       <c r="B1073" t="inlineStr">
         <is>
-          <t>OCT251072</t>
+          <t>OCT251409</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
